--- a/research/traditional_assets/database/data/latvia/latvia_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/latvia/latvia_construction_supplies.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="rise_rkb1r" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.349</v>
+        <v>-0.366</v>
       </c>
       <c r="G2">
-        <v>-0.05815602836879433</v>
+        <v>-0.07790697674418605</v>
       </c>
       <c r="H2">
-        <v>-0.05815602836879433</v>
+        <v>-0.07790697674418605</v>
       </c>
       <c r="I2">
-        <v>-0.1560283687943262</v>
+        <v>0.8197674418604651</v>
       </c>
       <c r="J2">
-        <v>-0.1560283687943262</v>
+        <v>0.8197674418604651</v>
       </c>
       <c r="K2">
-        <v>-0.395</v>
+        <v>1.37</v>
       </c>
       <c r="L2">
-        <v>-0.1400709219858156</v>
+        <v>0.7965116279069768</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.068</v>
+        <v>0.365</v>
       </c>
       <c r="V2">
-        <v>0.08651399491094147</v>
+        <v>0.5887096774193549</v>
       </c>
       <c r="W2">
-        <v>-0.03110236220472441</v>
+        <v>0.6372093023255815</v>
       </c>
       <c r="X2">
-        <v>0.2661472429499087</v>
+        <v>0.3865656477052053</v>
       </c>
       <c r="Y2">
-        <v>-0.2972496051546331</v>
+        <v>0.2506436546203762</v>
       </c>
       <c r="Z2">
-        <v>0.1718045570854149</v>
+        <v>0.2990264255910987</v>
       </c>
       <c r="AA2">
-        <v>-0.02680638479346899</v>
+        <v>0.2451321279554937</v>
       </c>
       <c r="AB2">
-        <v>0.07209789902975493</v>
+        <v>0.1104884983334254</v>
       </c>
       <c r="AC2">
-        <v>-0.09890428382322392</v>
+        <v>0.1346436296220682</v>
       </c>
       <c r="AD2">
-        <v>3.67</v>
+        <v>2.81</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.67</v>
+        <v>2.81</v>
       </c>
       <c r="AG2">
-        <v>3.602</v>
+        <v>2.445</v>
       </c>
       <c r="AH2">
-        <v>0.823608617594255</v>
+        <v>0.8192419825072886</v>
       </c>
       <c r="AI2">
-        <v>0.6305841924398625</v>
+        <v>0.4955908289241623</v>
       </c>
       <c r="AJ2">
-        <v>0.8208751139471285</v>
+        <v>0.797716150081566</v>
       </c>
       <c r="AK2">
-        <v>0.6262169680111266</v>
+        <v>0.4608859566446749</v>
       </c>
       <c r="AL2">
-        <v>0.025</v>
+        <v>0.073</v>
       </c>
       <c r="AM2">
-        <v>-0.04599999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AN2">
-        <v>-21.09195402298851</v>
+        <v>1.789808917197452</v>
       </c>
       <c r="AO2">
-        <v>-17.6</v>
+        <v>19.31506849315069</v>
       </c>
       <c r="AP2">
-        <v>-20.70114942528736</v>
+        <v>1.557324840764331</v>
       </c>
       <c r="AQ2">
-        <v>9.565217391304349</v>
+        <v>19.85915492957746</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.349</v>
+        <v>-0.366</v>
       </c>
       <c r="G3">
-        <v>-0.05815602836879433</v>
+        <v>-0.07790697674418605</v>
       </c>
       <c r="H3">
-        <v>-0.05815602836879433</v>
+        <v>-0.07790697674418605</v>
       </c>
       <c r="I3">
-        <v>-0.1560283687943262</v>
+        <v>0.8197674418604651</v>
       </c>
       <c r="J3">
-        <v>-0.1560283687943262</v>
+        <v>0.8197674418604651</v>
       </c>
       <c r="K3">
-        <v>-0.395</v>
+        <v>1.37</v>
       </c>
       <c r="L3">
-        <v>-0.1400709219858156</v>
+        <v>0.7965116279069768</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.068</v>
+        <v>0.365</v>
       </c>
       <c r="V3">
-        <v>0.08651399491094147</v>
+        <v>0.5887096774193549</v>
       </c>
       <c r="W3">
-        <v>-0.03110236220472441</v>
+        <v>0.6372093023255815</v>
       </c>
       <c r="X3">
-        <v>0.2661472429499087</v>
+        <v>0.3865656477052053</v>
       </c>
       <c r="Y3">
-        <v>-0.2972496051546331</v>
+        <v>0.2506436546203762</v>
       </c>
       <c r="Z3">
-        <v>0.1718045570854149</v>
+        <v>0.2990264255910987</v>
       </c>
       <c r="AA3">
-        <v>-0.02680638479346899</v>
+        <v>0.2451321279554937</v>
       </c>
       <c r="AB3">
-        <v>0.07209789902975493</v>
+        <v>0.1104884983334254</v>
       </c>
       <c r="AC3">
-        <v>-0.09890428382322392</v>
+        <v>0.1346436296220682</v>
       </c>
       <c r="AD3">
-        <v>3.67</v>
+        <v>2.81</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.67</v>
+        <v>2.81</v>
       </c>
       <c r="AG3">
-        <v>3.602</v>
+        <v>2.445</v>
       </c>
       <c r="AH3">
-        <v>0.823608617594255</v>
+        <v>0.8192419825072886</v>
       </c>
       <c r="AI3">
-        <v>0.6305841924398625</v>
+        <v>0.4955908289241623</v>
       </c>
       <c r="AJ3">
-        <v>0.8208751139471285</v>
+        <v>0.797716150081566</v>
       </c>
       <c r="AK3">
-        <v>0.6262169680111266</v>
+        <v>0.4608859566446749</v>
       </c>
       <c r="AL3">
-        <v>0.025</v>
+        <v>0.073</v>
       </c>
       <c r="AM3">
-        <v>-0.04599999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AN3">
-        <v>-21.09195402298851</v>
+        <v>1.789808917197452</v>
       </c>
       <c r="AO3">
-        <v>-17.6</v>
+        <v>19.31506849315069</v>
       </c>
       <c r="AP3">
-        <v>-20.70114942528736</v>
+        <v>1.557324840764331</v>
       </c>
       <c r="AQ3">
-        <v>9.565217391304349</v>
+        <v>19.85915492957746</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AS Rigas kugu buvetava (RISE:RKB1R)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RISE:RKB1R</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Construction Supplies</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.819241982507289</v>
+      </c>
+      <c r="F2">
+        <v>0.84</v>
+      </c>
+      <c r="G2">
+        <v>0.620000000000001</v>
+      </c>
+      <c r="H2">
+        <v>0.6689764525952669</v>
+      </c>
+      <c r="I2">
+        <v>3.065</v>
+      </c>
+      <c r="J2">
+        <v>3.18517645259527</v>
+      </c>
+      <c r="K2">
+        <v>2.81</v>
+      </c>
+      <c r="L2">
+        <v>2.8812</v>
+      </c>
+      <c r="M2">
+        <v>0.110488498333425</v>
+      </c>
+      <c r="N2">
+        <v>0.100542913707201</v>
+      </c>
+      <c r="O2">
+        <v>0.0495746788990826</v>
+      </c>
+      <c r="P2">
+        <v>0.03784</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.386565647705205</v>
+      </c>
+      <c r="T2">
+        <v>0.429733210670007</v>
+      </c>
+      <c r="U2">
+        <v>4.35611298801847</v>
+      </c>
+      <c r="V2">
+        <v>4.89682994190081</v>
+      </c>
+      <c r="W2">
+        <v>10.34628806003136</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>0.62</v>
+      </c>
+      <c r="AB2">
+        <v>0.07983393650755573</v>
+      </c>
+      <c r="AC2">
+        <v>0.06196834862385321</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1.57</v>
+      </c>
+      <c r="AH2">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>0.3339999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>2.81</v>
+      </c>
+      <c r="AK2">
+        <v>2.81</v>
+      </c>
+      <c r="AL2">
+        <v>0.073</v>
+      </c>
+      <c r="AM2">
+        <v>2.81</v>
+      </c>
+      <c r="AN2">
+        <v>0.365</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1139794635903861</v>
+      </c>
+      <c r="C2">
+        <v>3.389939370649186</v>
+      </c>
+      <c r="D2">
+        <v>3.024939370649186</v>
+      </c>
+      <c r="E2">
+        <v>-2.81</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.365</v>
+      </c>
+      <c r="H2">
+        <v>0.62</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.57</v>
+      </c>
+      <c r="K2">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L2">
+        <v>1.41</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.41</v>
+      </c>
+      <c r="O2">
+        <v>0.2819999999999999</v>
+      </c>
+      <c r="P2">
+        <v>1.128</v>
+      </c>
+      <c r="Q2">
+        <v>1.288</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1139794635903861</v>
+      </c>
+      <c r="T2">
+        <v>0.9416980657501568</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1138067046632053</v>
+      </c>
+      <c r="C3">
+        <v>3.357597222994483</v>
+      </c>
+      <c r="D3">
+        <v>3.026897222994484</v>
+      </c>
+      <c r="E3">
+        <v>-2.7757</v>
+      </c>
+      <c r="F3">
+        <v>0.0343</v>
+      </c>
+      <c r="G3">
+        <v>0.365</v>
+      </c>
+      <c r="H3">
+        <v>0.62</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.57</v>
+      </c>
+      <c r="K3">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L3">
+        <v>1.41</v>
+      </c>
+      <c r="M3">
+        <v>0.00156751</v>
+      </c>
+      <c r="N3">
+        <v>1.40843249</v>
+      </c>
+      <c r="O3">
+        <v>0.2816864979999999</v>
+      </c>
+      <c r="P3">
+        <v>1.126745992</v>
+      </c>
+      <c r="Q3">
+        <v>1.286745992</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1145869744072781</v>
+      </c>
+      <c r="T3">
+        <v>0.949307747089552</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>899.5157925627266</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1136339457360245</v>
+      </c>
+      <c r="C4">
+        <v>3.325257611369712</v>
+      </c>
+      <c r="D4">
+        <v>3.028857611369712</v>
+      </c>
+      <c r="E4">
+        <v>-2.7414</v>
+      </c>
+      <c r="F4">
+        <v>0.06860000000000001</v>
+      </c>
+      <c r="G4">
+        <v>0.365</v>
+      </c>
+      <c r="H4">
+        <v>0.62</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.57</v>
+      </c>
+      <c r="K4">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L4">
+        <v>1.41</v>
+      </c>
+      <c r="M4">
+        <v>0.003135020000000001</v>
+      </c>
+      <c r="N4">
+        <v>1.40686498</v>
+      </c>
+      <c r="O4">
+        <v>0.2813729959999999</v>
+      </c>
+      <c r="P4">
+        <v>1.125491984</v>
+      </c>
+      <c r="Q4">
+        <v>1.285491984</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1152068834041066</v>
+      </c>
+      <c r="T4">
+        <v>0.9570727280481185</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>449.7578962813633</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1134611868088437</v>
+      </c>
+      <c r="C5">
+        <v>3.292920540705492</v>
+      </c>
+      <c r="D5">
+        <v>3.030820540705491</v>
+      </c>
+      <c r="E5">
+        <v>-2.7071</v>
+      </c>
+      <c r="F5">
+        <v>0.1029</v>
+      </c>
+      <c r="G5">
+        <v>0.365</v>
+      </c>
+      <c r="H5">
+        <v>0.62</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.57</v>
+      </c>
+      <c r="K5">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L5">
+        <v>1.41</v>
+      </c>
+      <c r="M5">
+        <v>0.004702530000000001</v>
+      </c>
+      <c r="N5">
+        <v>1.40529747</v>
+      </c>
+      <c r="O5">
+        <v>0.2810594939999999</v>
+      </c>
+      <c r="P5">
+        <v>1.124237976</v>
+      </c>
+      <c r="Q5">
+        <v>1.284237976</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1158395740297358</v>
+      </c>
+      <c r="T5">
+        <v>0.9649978117068616</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>299.8385975209089</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.113288427881663</v>
+      </c>
+      <c r="C6">
+        <v>3.260586015945228</v>
+      </c>
+      <c r="D6">
+        <v>3.032786015945228</v>
+      </c>
+      <c r="E6">
+        <v>-2.6728</v>
+      </c>
+      <c r="F6">
+        <v>0.1372</v>
+      </c>
+      <c r="G6">
+        <v>0.365</v>
+      </c>
+      <c r="H6">
+        <v>0.62</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.57</v>
+      </c>
+      <c r="K6">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L6">
+        <v>1.41</v>
+      </c>
+      <c r="M6">
+        <v>0.006270040000000001</v>
+      </c>
+      <c r="N6">
+        <v>1.40372996</v>
+      </c>
+      <c r="O6">
+        <v>0.2807459919999999</v>
+      </c>
+      <c r="P6">
+        <v>1.122983968</v>
+      </c>
+      <c r="Q6">
+        <v>1.282983968</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1164854457100656</v>
+      </c>
+      <c r="T6">
+        <v>0.9730880012751622</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03656</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>224.8789481406817</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1131156689544822</v>
+      </c>
+      <c r="C7">
+        <v>3.228254042045166</v>
+      </c>
+      <c r="D7">
+        <v>3.034754042045166</v>
+      </c>
+      <c r="E7">
+        <v>-2.6385</v>
+      </c>
+      <c r="F7">
+        <v>0.1715</v>
+      </c>
+      <c r="G7">
+        <v>0.365</v>
+      </c>
+      <c r="H7">
+        <v>0.62</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.57</v>
+      </c>
+      <c r="K7">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L7">
+        <v>1.41</v>
+      </c>
+      <c r="M7">
+        <v>0.007837550000000002</v>
+      </c>
+      <c r="N7">
+        <v>1.40216245</v>
+      </c>
+      <c r="O7">
+        <v>0.2804324899999999</v>
+      </c>
+      <c r="P7">
+        <v>1.12172996</v>
+      </c>
+      <c r="Q7">
+        <v>1.28172996</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1171449146889286</v>
+      </c>
+      <c r="T7">
+        <v>0.9813485106238475</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03656</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>179.9031585125453</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1129429100273014</v>
+      </c>
+      <c r="C8">
+        <v>3.195924623974416</v>
+      </c>
+      <c r="D8">
+        <v>3.036724623974416</v>
+      </c>
+      <c r="E8">
+        <v>-2.6042</v>
+      </c>
+      <c r="F8">
+        <v>0.2058</v>
+      </c>
+      <c r="G8">
+        <v>0.365</v>
+      </c>
+      <c r="H8">
+        <v>0.62</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.57</v>
+      </c>
+      <c r="K8">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L8">
+        <v>1.41</v>
+      </c>
+      <c r="M8">
+        <v>0.009405060000000002</v>
+      </c>
+      <c r="N8">
+        <v>1.40059494</v>
+      </c>
+      <c r="O8">
+        <v>0.2801189879999999</v>
+      </c>
+      <c r="P8">
+        <v>1.120475952</v>
+      </c>
+      <c r="Q8">
+        <v>1.280475952</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1178184149226611</v>
+      </c>
+      <c r="T8">
+        <v>0.9897847754905904</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03656</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>149.9192987604544</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1127701511001207</v>
+      </c>
+      <c r="C9">
+        <v>3.163597766715006</v>
+      </c>
+      <c r="D9">
+        <v>3.038697766715007</v>
+      </c>
+      <c r="E9">
+        <v>-2.5699</v>
+      </c>
+      <c r="F9">
+        <v>0.2401</v>
+      </c>
+      <c r="G9">
+        <v>0.365</v>
+      </c>
+      <c r="H9">
+        <v>0.62</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.57</v>
+      </c>
+      <c r="K9">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L9">
+        <v>1.41</v>
+      </c>
+      <c r="M9">
+        <v>0.01097257</v>
+      </c>
+      <c r="N9">
+        <v>1.39902743</v>
+      </c>
+      <c r="O9">
+        <v>0.2798054859999999</v>
+      </c>
+      <c r="P9">
+        <v>1.119221944</v>
+      </c>
+      <c r="Q9">
+        <v>1.279221944</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1185063990323878</v>
+      </c>
+      <c r="T9">
+        <v>0.9984024654082309</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03656</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>128.5022560803895</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1125973921729399</v>
+      </c>
+      <c r="C10">
+        <v>3.131273475261924</v>
+      </c>
+      <c r="D10">
+        <v>3.040673475261924</v>
+      </c>
+      <c r="E10">
+        <v>-2.5356</v>
+      </c>
+      <c r="F10">
+        <v>0.2744</v>
+      </c>
+      <c r="G10">
+        <v>0.365</v>
+      </c>
+      <c r="H10">
+        <v>0.62</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.57</v>
+      </c>
+      <c r="K10">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L10">
+        <v>1.41</v>
+      </c>
+      <c r="M10">
+        <v>0.01254008</v>
+      </c>
+      <c r="N10">
+        <v>1.39745992</v>
+      </c>
+      <c r="O10">
+        <v>0.2794919839999999</v>
+      </c>
+      <c r="P10">
+        <v>1.117967936</v>
+      </c>
+      <c r="Q10">
+        <v>1.277967936</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1192093393184129</v>
+      </c>
+      <c r="T10">
+        <v>1.007207496411037</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03656</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>112.4394740703408</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1124246332457591</v>
+      </c>
+      <c r="C11">
+        <v>3.098951754623152</v>
+      </c>
+      <c r="D11">
+        <v>3.042651754623152</v>
+      </c>
+      <c r="E11">
+        <v>-2.5013</v>
+      </c>
+      <c r="F11">
+        <v>0.3087</v>
+      </c>
+      <c r="G11">
+        <v>0.365</v>
+      </c>
+      <c r="H11">
+        <v>0.62</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.57</v>
+      </c>
+      <c r="K11">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L11">
+        <v>1.41</v>
+      </c>
+      <c r="M11">
+        <v>0.01410759</v>
+      </c>
+      <c r="N11">
+        <v>1.39589241</v>
+      </c>
+      <c r="O11">
+        <v>0.2791784819999999</v>
+      </c>
+      <c r="P11">
+        <v>1.116713928</v>
+      </c>
+      <c r="Q11">
+        <v>1.276713928</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1199277288414935</v>
+      </c>
+      <c r="T11">
+        <v>1.016206044578741</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03656</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>99.94619917363629</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1122518743185784</v>
+      </c>
+      <c r="C12">
+        <v>3.066632609819717</v>
+      </c>
+      <c r="D12">
+        <v>3.044632609819717</v>
+      </c>
+      <c r="E12">
+        <v>-2.467</v>
+      </c>
+      <c r="F12">
+        <v>0.343</v>
+      </c>
+      <c r="G12">
+        <v>0.365</v>
+      </c>
+      <c r="H12">
+        <v>0.62</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.57</v>
+      </c>
+      <c r="K12">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L12">
+        <v>1.41</v>
+      </c>
+      <c r="M12">
+        <v>0.0156751</v>
+      </c>
+      <c r="N12">
+        <v>1.3943249</v>
+      </c>
+      <c r="O12">
+        <v>0.2788649799999999</v>
+      </c>
+      <c r="P12">
+        <v>1.11545992</v>
+      </c>
+      <c r="Q12">
+        <v>1.27545992</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1206620825761982</v>
+      </c>
+      <c r="T12">
+        <v>1.025404560483504</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03656</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>89.95157925627267</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1120791153913976</v>
+      </c>
+      <c r="C13">
+        <v>3.034316045885728</v>
+      </c>
+      <c r="D13">
+        <v>3.046616045885727</v>
+      </c>
+      <c r="E13">
+        <v>-2.4327</v>
+      </c>
+      <c r="F13">
+        <v>0.3773</v>
+      </c>
+      <c r="G13">
+        <v>0.365</v>
+      </c>
+      <c r="H13">
+        <v>0.62</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.57</v>
+      </c>
+      <c r="K13">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L13">
+        <v>1.41</v>
+      </c>
+      <c r="M13">
+        <v>0.01724261</v>
+      </c>
+      <c r="N13">
+        <v>1.39275739</v>
+      </c>
+      <c r="O13">
+        <v>0.2785514779999999</v>
+      </c>
+      <c r="P13">
+        <v>1.114205912</v>
+      </c>
+      <c r="Q13">
+        <v>1.274205912</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1214129386420197</v>
+      </c>
+      <c r="T13">
+        <v>1.034809784610846</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03656</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>81.77416296024788</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1119063564642168</v>
+      </c>
+      <c r="C14">
+        <v>3.002002067868419</v>
+      </c>
+      <c r="D14">
+        <v>3.04860206786842</v>
+      </c>
+      <c r="E14">
+        <v>-2.3984</v>
+      </c>
+      <c r="F14">
+        <v>0.4116</v>
+      </c>
+      <c r="G14">
+        <v>0.365</v>
+      </c>
+      <c r="H14">
+        <v>0.62</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.57</v>
+      </c>
+      <c r="K14">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L14">
+        <v>1.41</v>
+      </c>
+      <c r="M14">
+        <v>0.01881012</v>
+      </c>
+      <c r="N14">
+        <v>1.39118988</v>
+      </c>
+      <c r="O14">
+        <v>0.2782379759999999</v>
+      </c>
+      <c r="P14">
+        <v>1.112951904</v>
+      </c>
+      <c r="Q14">
+        <v>1.272951904</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1221808596184282</v>
+      </c>
+      <c r="T14">
+        <v>1.044428763831992</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03656</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>74.95964938022723</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.111733597537036</v>
+      </c>
+      <c r="C15">
+        <v>2.9696906808282</v>
+      </c>
+      <c r="D15">
+        <v>3.0505906808282</v>
+      </c>
+      <c r="E15">
+        <v>-2.3641</v>
+      </c>
+      <c r="F15">
+        <v>0.4459</v>
+      </c>
+      <c r="G15">
+        <v>0.365</v>
+      </c>
+      <c r="H15">
+        <v>0.62</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.57</v>
+      </c>
+      <c r="K15">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L15">
+        <v>1.41</v>
+      </c>
+      <c r="M15">
+        <v>0.02037763</v>
+      </c>
+      <c r="N15">
+        <v>1.38962237</v>
+      </c>
+      <c r="O15">
+        <v>0.2779244739999999</v>
+      </c>
+      <c r="P15">
+        <v>1.111697896</v>
+      </c>
+      <c r="Q15">
+        <v>1.271697896</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1229664339506161</v>
+      </c>
+      <c r="T15">
+        <v>1.054268869012244</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.03656</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>69.19352250482513</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1115608386098552</v>
+      </c>
+      <c r="C16">
+        <v>2.937381889838685</v>
+      </c>
+      <c r="D16">
+        <v>3.052581889838685</v>
+      </c>
+      <c r="E16">
+        <v>-2.3298</v>
+      </c>
+      <c r="F16">
+        <v>0.4802000000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.365</v>
+      </c>
+      <c r="H16">
+        <v>0.62</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.57</v>
+      </c>
+      <c r="K16">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L16">
+        <v>1.41</v>
+      </c>
+      <c r="M16">
+        <v>0.02194514000000001</v>
+      </c>
+      <c r="N16">
+        <v>1.38805486</v>
+      </c>
+      <c r="O16">
+        <v>0.277610972</v>
+      </c>
+      <c r="P16">
+        <v>1.110443888</v>
+      </c>
+      <c r="Q16">
+        <v>1.270443888</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1237702774533201</v>
+      </c>
+      <c r="T16">
+        <v>1.064337813847852</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.03656</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>64.25112804019477</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1113880796826745</v>
+      </c>
+      <c r="C17">
+        <v>2.905075699986748</v>
+      </c>
+      <c r="D17">
+        <v>3.054575699986747</v>
+      </c>
+      <c r="E17">
+        <v>-2.2955</v>
+      </c>
+      <c r="F17">
+        <v>0.5145</v>
+      </c>
+      <c r="G17">
+        <v>0.365</v>
+      </c>
+      <c r="H17">
+        <v>0.62</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.57</v>
+      </c>
+      <c r="K17">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L17">
+        <v>1.41</v>
+      </c>
+      <c r="M17">
+        <v>0.02351265</v>
+      </c>
+      <c r="N17">
+        <v>1.38648735</v>
+      </c>
+      <c r="O17">
+        <v>0.2772974699999999</v>
+      </c>
+      <c r="P17">
+        <v>1.10918988</v>
+      </c>
+      <c r="Q17">
+        <v>1.26918988</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1245930349207935</v>
+      </c>
+      <c r="T17">
+        <v>1.074643675032532</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.03656</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>59.96771950418179</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1112153207554937</v>
+      </c>
+      <c r="C18">
+        <v>2.872772116372561</v>
+      </c>
+      <c r="D18">
+        <v>3.056572116372561</v>
+      </c>
+      <c r="E18">
+        <v>-2.2612</v>
+      </c>
+      <c r="F18">
+        <v>0.5488000000000001</v>
+      </c>
+      <c r="G18">
+        <v>0.365</v>
+      </c>
+      <c r="H18">
+        <v>0.62</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.57</v>
+      </c>
+      <c r="K18">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L18">
+        <v>1.41</v>
+      </c>
+      <c r="M18">
+        <v>0.02508016</v>
+      </c>
+      <c r="N18">
+        <v>1.38491984</v>
+      </c>
+      <c r="O18">
+        <v>0.2769839679999999</v>
+      </c>
+      <c r="P18">
+        <v>1.107935872</v>
+      </c>
+      <c r="Q18">
+        <v>1.267935872</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1254353818517782</v>
+      </c>
+      <c r="T18">
+        <v>1.085194913864466</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.03656</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>56.21973703517042</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1110425618283129</v>
+      </c>
+      <c r="C19">
+        <v>2.840471144109638</v>
+      </c>
+      <c r="D19">
+        <v>3.058571144109638</v>
+      </c>
+      <c r="E19">
+        <v>-2.2269</v>
+      </c>
+      <c r="F19">
+        <v>0.5831000000000001</v>
+      </c>
+      <c r="G19">
+        <v>0.365</v>
+      </c>
+      <c r="H19">
+        <v>0.62</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.57</v>
+      </c>
+      <c r="K19">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L19">
+        <v>1.41</v>
+      </c>
+      <c r="M19">
+        <v>0.02664767000000001</v>
+      </c>
+      <c r="N19">
+        <v>1.38335233</v>
+      </c>
+      <c r="O19">
+        <v>0.2766704659999999</v>
+      </c>
+      <c r="P19">
+        <v>1.106681864</v>
+      </c>
+      <c r="Q19">
+        <v>1.266681864</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1262980262991722</v>
+      </c>
+      <c r="T19">
+        <v>1.096000399415243</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.03656</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>52.91269368016039</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1108698029011322</v>
+      </c>
+      <c r="C20">
+        <v>2.808172788324878</v>
+      </c>
+      <c r="D20">
+        <v>3.060572788324878</v>
+      </c>
+      <c r="E20">
+        <v>-2.1926</v>
+      </c>
+      <c r="F20">
+        <v>0.6174000000000001</v>
+      </c>
+      <c r="G20">
+        <v>0.365</v>
+      </c>
+      <c r="H20">
+        <v>0.62</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.57</v>
+      </c>
+      <c r="K20">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L20">
+        <v>1.41</v>
+      </c>
+      <c r="M20">
+        <v>0.02821518000000001</v>
+      </c>
+      <c r="N20">
+        <v>1.38178482</v>
+      </c>
+      <c r="O20">
+        <v>0.2763569639999999</v>
+      </c>
+      <c r="P20">
+        <v>1.105427856</v>
+      </c>
+      <c r="Q20">
+        <v>1.265427856</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1271817108550392</v>
+      </c>
+      <c r="T20">
+        <v>1.107069433394087</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.03656</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>49.97309958681815</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1106970439739514</v>
+      </c>
+      <c r="C21">
+        <v>2.775877054158613</v>
+      </c>
+      <c r="D21">
+        <v>3.062577054158613</v>
+      </c>
+      <c r="E21">
+        <v>-2.1583</v>
+      </c>
+      <c r="F21">
+        <v>0.6517000000000001</v>
+      </c>
+      <c r="G21">
+        <v>0.365</v>
+      </c>
+      <c r="H21">
+        <v>0.62</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.57</v>
+      </c>
+      <c r="K21">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L21">
+        <v>1.41</v>
+      </c>
+      <c r="M21">
+        <v>0.02978269</v>
+      </c>
+      <c r="N21">
+        <v>1.38021731</v>
+      </c>
+      <c r="O21">
+        <v>0.2760434619999999</v>
+      </c>
+      <c r="P21">
+        <v>1.104173848</v>
+      </c>
+      <c r="Q21">
+        <v>1.264173848</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1280872147826561</v>
+      </c>
+      <c r="T21">
+        <v>1.11841177685389</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.03656</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>47.34293645066982</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1105242850467706</v>
+      </c>
+      <c r="C22">
+        <v>2.743583946764646</v>
+      </c>
+      <c r="D22">
+        <v>3.064583946764647</v>
+      </c>
+      <c r="E22">
+        <v>-2.124</v>
+      </c>
+      <c r="F22">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.365</v>
+      </c>
+      <c r="H22">
+        <v>0.62</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.57</v>
+      </c>
+      <c r="K22">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L22">
+        <v>1.41</v>
+      </c>
+      <c r="M22">
+        <v>0.03135020000000001</v>
+      </c>
+      <c r="N22">
+        <v>1.3786498</v>
+      </c>
+      <c r="O22">
+        <v>0.2757299599999999</v>
+      </c>
+      <c r="P22">
+        <v>1.10291984</v>
+      </c>
+      <c r="Q22">
+        <v>1.26291984</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1290153563084633</v>
+      </c>
+      <c r="T22">
+        <v>1.130037678900188</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.03656</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>44.97578962813633</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1103515261195898</v>
+      </c>
+      <c r="C23">
+        <v>2.711293471310298</v>
+      </c>
+      <c r="D23">
+        <v>3.066593471310298</v>
+      </c>
+      <c r="E23">
+        <v>-2.0897</v>
+      </c>
+      <c r="F23">
+        <v>0.7203000000000001</v>
+      </c>
+      <c r="G23">
+        <v>0.365</v>
+      </c>
+      <c r="H23">
+        <v>0.62</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.57</v>
+      </c>
+      <c r="K23">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L23">
+        <v>1.41</v>
+      </c>
+      <c r="M23">
+        <v>0.03291771</v>
+      </c>
+      <c r="N23">
+        <v>1.37708229</v>
+      </c>
+      <c r="O23">
+        <v>0.2754164579999999</v>
+      </c>
+      <c r="P23">
+        <v>1.101665832</v>
+      </c>
+      <c r="Q23">
+        <v>1.261665832</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1299669950880884</v>
+      </c>
+      <c r="T23">
+        <v>1.14195790758057</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.03656</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>42.83408536012985</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1101787671924091</v>
+      </c>
+      <c r="C24">
+        <v>2.679005632976451</v>
+      </c>
+      <c r="D24">
+        <v>3.068605632976451</v>
+      </c>
+      <c r="E24">
+        <v>-2.0554</v>
+      </c>
+      <c r="F24">
+        <v>0.7546</v>
+      </c>
+      <c r="G24">
+        <v>0.365</v>
+      </c>
+      <c r="H24">
+        <v>0.62</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.57</v>
+      </c>
+      <c r="K24">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L24">
+        <v>1.41</v>
+      </c>
+      <c r="M24">
+        <v>0.03448522</v>
+      </c>
+      <c r="N24">
+        <v>1.37551478</v>
+      </c>
+      <c r="O24">
+        <v>0.2751029559999999</v>
+      </c>
+      <c r="P24">
+        <v>1.100411824</v>
+      </c>
+      <c r="Q24">
+        <v>1.260411824</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1309430348620629</v>
+      </c>
+      <c r="T24">
+        <v>1.154183783150192</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.03656</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>40.88708148012394</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1100060082652283</v>
+      </c>
+      <c r="C25">
+        <v>2.646720436957598</v>
+      </c>
+      <c r="D25">
+        <v>3.070620436957598</v>
+      </c>
+      <c r="E25">
+        <v>-2.0211</v>
+      </c>
+      <c r="F25">
+        <v>0.7889</v>
+      </c>
+      <c r="G25">
+        <v>0.365</v>
+      </c>
+      <c r="H25">
+        <v>0.62</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.57</v>
+      </c>
+      <c r="K25">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L25">
+        <v>1.41</v>
+      </c>
+      <c r="M25">
+        <v>0.03605273000000001</v>
+      </c>
+      <c r="N25">
+        <v>1.37394727</v>
+      </c>
+      <c r="O25">
+        <v>0.2747894539999999</v>
+      </c>
+      <c r="P25">
+        <v>1.099157816</v>
+      </c>
+      <c r="Q25">
+        <v>1.259157816</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1319444263184783</v>
+      </c>
+      <c r="T25">
+        <v>1.166727213929415</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.03656</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>39.10938228533595</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1098332493380475</v>
+      </c>
+      <c r="C26">
+        <v>2.61443788846188</v>
+      </c>
+      <c r="D26">
+        <v>3.07263788846188</v>
+      </c>
+      <c r="E26">
+        <v>-1.9868</v>
+      </c>
+      <c r="F26">
+        <v>0.8232</v>
+      </c>
+      <c r="G26">
+        <v>0.365</v>
+      </c>
+      <c r="H26">
+        <v>0.62</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.57</v>
+      </c>
+      <c r="K26">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L26">
+        <v>1.41</v>
+      </c>
+      <c r="M26">
+        <v>0.03762024000000001</v>
+      </c>
+      <c r="N26">
+        <v>1.37237976</v>
+      </c>
+      <c r="O26">
+        <v>0.2744759519999999</v>
+      </c>
+      <c r="P26">
+        <v>1.097903808</v>
+      </c>
+      <c r="Q26">
+        <v>1.257903808</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1329721701816415</v>
+      </c>
+      <c r="T26">
+        <v>1.179600734992302</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.03656</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>37.47982469011361</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1096604904108668</v>
+      </c>
+      <c r="C27">
+        <v>2.582157992711134</v>
+      </c>
+      <c r="D27">
+        <v>3.074657992711134</v>
+      </c>
+      <c r="E27">
+        <v>-1.9525</v>
+      </c>
+      <c r="F27">
+        <v>0.8575</v>
+      </c>
+      <c r="G27">
+        <v>0.365</v>
+      </c>
+      <c r="H27">
+        <v>0.62</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.57</v>
+      </c>
+      <c r="K27">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L27">
+        <v>1.41</v>
+      </c>
+      <c r="M27">
+        <v>0.03918775000000001</v>
+      </c>
+      <c r="N27">
+        <v>1.37081225</v>
+      </c>
+      <c r="O27">
+        <v>0.2741624499999999</v>
+      </c>
+      <c r="P27">
+        <v>1.0966498</v>
+      </c>
+      <c r="Q27">
+        <v>1.2566498</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1340273205478223</v>
+      </c>
+      <c r="T27">
+        <v>1.192817549950199</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.03656</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>35.98063170250906</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.109487731483686</v>
+      </c>
+      <c r="C28">
+        <v>2.549880754940942</v>
+      </c>
+      <c r="D28">
+        <v>3.076680754940942</v>
+      </c>
+      <c r="E28">
+        <v>-1.9182</v>
+      </c>
+      <c r="F28">
+        <v>0.8918</v>
+      </c>
+      <c r="G28">
+        <v>0.365</v>
+      </c>
+      <c r="H28">
+        <v>0.62</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.57</v>
+      </c>
+      <c r="K28">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L28">
+        <v>1.41</v>
+      </c>
+      <c r="M28">
+        <v>0.04075526000000001</v>
+      </c>
+      <c r="N28">
+        <v>1.36924474</v>
+      </c>
+      <c r="O28">
+        <v>0.2738489479999999</v>
+      </c>
+      <c r="P28">
+        <v>1.095395792</v>
+      </c>
+      <c r="Q28">
+        <v>1.255395792</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1351109884914675</v>
+      </c>
+      <c r="T28">
+        <v>1.206391576123174</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.03656</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>34.59676125241256</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1093149725565052</v>
+      </c>
+      <c r="C29">
+        <v>2.517606180400669</v>
+      </c>
+      <c r="D29">
+        <v>3.078706180400669</v>
+      </c>
+      <c r="E29">
+        <v>-1.8839</v>
+      </c>
+      <c r="F29">
+        <v>0.9261000000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.365</v>
+      </c>
+      <c r="H29">
+        <v>0.62</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.57</v>
+      </c>
+      <c r="K29">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L29">
+        <v>1.41</v>
+      </c>
+      <c r="M29">
+        <v>0.04232277000000001</v>
+      </c>
+      <c r="N29">
+        <v>1.36767723</v>
+      </c>
+      <c r="O29">
+        <v>0.273535446</v>
+      </c>
+      <c r="P29">
+        <v>1.094141784</v>
+      </c>
+      <c r="Q29">
+        <v>1.254141784</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1362243459678154</v>
+      </c>
+      <c r="T29">
+        <v>1.220337493424176</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.03656</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>33.31539972454543</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1091422136293244</v>
+      </c>
+      <c r="C30">
+        <v>2.485334274353513</v>
+      </c>
+      <c r="D30">
+        <v>3.080734274353513</v>
+      </c>
+      <c r="E30">
+        <v>-1.8496</v>
+      </c>
+      <c r="F30">
+        <v>0.9604000000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.365</v>
+      </c>
+      <c r="H30">
+        <v>0.62</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.57</v>
+      </c>
+      <c r="K30">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L30">
+        <v>1.41</v>
+      </c>
+      <c r="M30">
+        <v>0.04389028000000001</v>
+      </c>
+      <c r="N30">
+        <v>1.36610972</v>
+      </c>
+      <c r="O30">
+        <v>0.2732219439999999</v>
+      </c>
+      <c r="P30">
+        <v>1.092887776</v>
+      </c>
+      <c r="Q30">
+        <v>1.252887776</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1373686300407284</v>
+      </c>
+      <c r="T30">
+        <v>1.234670797316872</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.03656</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>32.12556402009738</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1089694547021437</v>
+      </c>
+      <c r="C31">
+        <v>2.453065042076552</v>
+      </c>
+      <c r="D31">
+        <v>3.082765042076551</v>
+      </c>
+      <c r="E31">
+        <v>-1.8153</v>
+      </c>
+      <c r="F31">
+        <v>0.9947</v>
+      </c>
+      <c r="G31">
+        <v>0.365</v>
+      </c>
+      <c r="H31">
+        <v>0.62</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.57</v>
+      </c>
+      <c r="K31">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L31">
+        <v>1.41</v>
+      </c>
+      <c r="M31">
+        <v>0.04545779</v>
+      </c>
+      <c r="N31">
+        <v>1.36454221</v>
+      </c>
+      <c r="O31">
+        <v>0.2729084419999999</v>
+      </c>
+      <c r="P31">
+        <v>1.091633768</v>
+      </c>
+      <c r="Q31">
+        <v>1.251633768</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.138545147467808</v>
+      </c>
+      <c r="T31">
+        <v>1.2494078562488</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.03656</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>31.01778595043885</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1087966957749629</v>
+      </c>
+      <c r="C32">
+        <v>2.420798488860783</v>
+      </c>
+      <c r="D32">
+        <v>3.084798488860783</v>
+      </c>
+      <c r="E32">
+        <v>-1.781</v>
+      </c>
+      <c r="F32">
+        <v>1.029</v>
+      </c>
+      <c r="G32">
+        <v>0.365</v>
+      </c>
+      <c r="H32">
+        <v>0.62</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.57</v>
+      </c>
+      <c r="K32">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L32">
+        <v>1.41</v>
+      </c>
+      <c r="M32">
+        <v>0.0470253</v>
+      </c>
+      <c r="N32">
+        <v>1.3629747</v>
+      </c>
+      <c r="O32">
+        <v>0.2725949399999999</v>
+      </c>
+      <c r="P32">
+        <v>1.09037976</v>
+      </c>
+      <c r="Q32">
+        <v>1.25037976</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1397552796785184</v>
+      </c>
+      <c r="T32">
+        <v>1.264565974007354</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.03656</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>29.98385975209089</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1086239368477821</v>
+      </c>
+      <c r="C33">
+        <v>2.388534620011177</v>
+      </c>
+      <c r="D33">
+        <v>3.086834620011176</v>
+      </c>
+      <c r="E33">
+        <v>-1.7467</v>
+      </c>
+      <c r="F33">
+        <v>1.0633</v>
+      </c>
+      <c r="G33">
+        <v>0.365</v>
+      </c>
+      <c r="H33">
+        <v>0.62</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.57</v>
+      </c>
+      <c r="K33">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L33">
+        <v>1.41</v>
+      </c>
+      <c r="M33">
+        <v>0.04859281000000001</v>
+      </c>
+      <c r="N33">
+        <v>1.36140719</v>
+      </c>
+      <c r="O33">
+        <v>0.2722814379999999</v>
+      </c>
+      <c r="P33">
+        <v>1.089125752</v>
+      </c>
+      <c r="Q33">
+        <v>1.249125752</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1410004881851915</v>
+      </c>
+      <c r="T33">
+        <v>1.280163457498039</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.03656</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>29.01663846976538</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1084511779206014</v>
+      </c>
+      <c r="C34">
+        <v>2.356273440846715</v>
+      </c>
+      <c r="D34">
+        <v>3.088873440846716</v>
+      </c>
+      <c r="E34">
+        <v>-1.7124</v>
+      </c>
+      <c r="F34">
+        <v>1.0976</v>
+      </c>
+      <c r="G34">
+        <v>0.365</v>
+      </c>
+      <c r="H34">
+        <v>0.62</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.57</v>
+      </c>
+      <c r="K34">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L34">
+        <v>1.41</v>
+      </c>
+      <c r="M34">
+        <v>0.05016032000000001</v>
+      </c>
+      <c r="N34">
+        <v>1.35983968</v>
+      </c>
+      <c r="O34">
+        <v>0.2719679359999999</v>
+      </c>
+      <c r="P34">
+        <v>1.087871744</v>
+      </c>
+      <c r="Q34">
+        <v>1.247871744</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1422823204714726</v>
+      </c>
+      <c r="T34">
+        <v>1.296219690503157</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.03656</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>28.10986851758521</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1082784189934206</v>
+      </c>
+      <c r="C35">
+        <v>2.324014956700449</v>
+      </c>
+      <c r="D35">
+        <v>3.090914956700448</v>
+      </c>
+      <c r="E35">
+        <v>-1.6781</v>
+      </c>
+      <c r="F35">
+        <v>1.1319</v>
+      </c>
+      <c r="G35">
+        <v>0.365</v>
+      </c>
+      <c r="H35">
+        <v>0.62</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.57</v>
+      </c>
+      <c r="K35">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L35">
+        <v>1.41</v>
+      </c>
+      <c r="M35">
+        <v>0.05172783000000001</v>
+      </c>
+      <c r="N35">
+        <v>1.35827217</v>
+      </c>
+      <c r="O35">
+        <v>0.2716544339999999</v>
+      </c>
+      <c r="P35">
+        <v>1.086617736</v>
+      </c>
+      <c r="Q35">
+        <v>1.246617736</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1436024164080904</v>
+      </c>
+      <c r="T35">
+        <v>1.312755214045741</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.03656</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>27.25805432008263</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1081056600662398</v>
+      </c>
+      <c r="C36">
+        <v>2.291759172919527</v>
+      </c>
+      <c r="D36">
+        <v>3.092959172919528</v>
+      </c>
+      <c r="E36">
+        <v>-1.6438</v>
+      </c>
+      <c r="F36">
+        <v>1.1662</v>
+      </c>
+      <c r="G36">
+        <v>0.365</v>
+      </c>
+      <c r="H36">
+        <v>0.62</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.57</v>
+      </c>
+      <c r="K36">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L36">
+        <v>1.41</v>
+      </c>
+      <c r="M36">
+        <v>0.05329534000000001</v>
+      </c>
+      <c r="N36">
+        <v>1.35670466</v>
+      </c>
+      <c r="O36">
+        <v>0.2713409319999999</v>
+      </c>
+      <c r="P36">
+        <v>1.085363728</v>
+      </c>
+      <c r="Q36">
+        <v>1.245363728</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1449625152518785</v>
+      </c>
+      <c r="T36">
+        <v>1.329791814059312</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.03656</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>26.45634684008019</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.107932901139059</v>
+      </c>
+      <c r="C37">
+        <v>2.259506094865262</v>
+      </c>
+      <c r="D37">
+        <v>3.095006094865262</v>
+      </c>
+      <c r="E37">
+        <v>-1.6095</v>
+      </c>
+      <c r="F37">
+        <v>1.2005</v>
+      </c>
+      <c r="G37">
+        <v>0.365</v>
+      </c>
+      <c r="H37">
+        <v>0.62</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.57</v>
+      </c>
+      <c r="K37">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L37">
+        <v>1.41</v>
+      </c>
+      <c r="M37">
+        <v>0.05486285000000001</v>
+      </c>
+      <c r="N37">
+        <v>1.35513715</v>
+      </c>
+      <c r="O37">
+        <v>0.27102743</v>
+      </c>
+      <c r="P37">
+        <v>1.08410972</v>
+      </c>
+      <c r="Q37">
+        <v>1.24410972</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1463644632908601</v>
+      </c>
+      <c r="T37">
+        <v>1.347352617150224</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.03656</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>25.70045121607791</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1077601422118783</v>
+      </c>
+      <c r="C38">
+        <v>2.227255727913166</v>
+      </c>
+      <c r="D38">
+        <v>3.097055727913165</v>
+      </c>
+      <c r="E38">
+        <v>-1.5752</v>
+      </c>
+      <c r="F38">
+        <v>1.2348</v>
+      </c>
+      <c r="G38">
+        <v>0.365</v>
+      </c>
+      <c r="H38">
+        <v>0.62</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.57</v>
+      </c>
+      <c r="K38">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L38">
+        <v>1.41</v>
+      </c>
+      <c r="M38">
+        <v>0.05643036000000001</v>
+      </c>
+      <c r="N38">
+        <v>1.35356964</v>
+      </c>
+      <c r="O38">
+        <v>0.2707139279999999</v>
+      </c>
+      <c r="P38">
+        <v>1.082855712</v>
+      </c>
+      <c r="Q38">
+        <v>1.242855712</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1478102222060598</v>
+      </c>
+      <c r="T38">
+        <v>1.365462195337727</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.03656</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>24.98654979340907</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1075873832846975</v>
+      </c>
+      <c r="C39">
+        <v>2.195008077452997</v>
+      </c>
+      <c r="D39">
+        <v>3.099108077452997</v>
+      </c>
+      <c r="E39">
+        <v>-1.5409</v>
+      </c>
+      <c r="F39">
+        <v>1.2691</v>
+      </c>
+      <c r="G39">
+        <v>0.365</v>
+      </c>
+      <c r="H39">
+        <v>0.62</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.57</v>
+      </c>
+      <c r="K39">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L39">
+        <v>1.41</v>
+      </c>
+      <c r="M39">
+        <v>0.05799787000000001</v>
+      </c>
+      <c r="N39">
+        <v>1.35200213</v>
+      </c>
+      <c r="O39">
+        <v>0.2704004259999999</v>
+      </c>
+      <c r="P39">
+        <v>1.081601704</v>
+      </c>
+      <c r="Q39">
+        <v>1.241601704</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1493018782296786</v>
+      </c>
+      <c r="T39">
+        <v>1.384146680769278</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.03656</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>24.31123763683045</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1074146243575167</v>
+      </c>
+      <c r="C40">
+        <v>2.162763148888812</v>
+      </c>
+      <c r="D40">
+        <v>3.101163148888813</v>
+      </c>
+      <c r="E40">
+        <v>-1.5066</v>
+      </c>
+      <c r="F40">
+        <v>1.3034</v>
+      </c>
+      <c r="G40">
+        <v>0.365</v>
+      </c>
+      <c r="H40">
+        <v>0.62</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.57</v>
+      </c>
+      <c r="K40">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L40">
+        <v>1.41</v>
+      </c>
+      <c r="M40">
+        <v>0.05956538000000001</v>
+      </c>
+      <c r="N40">
+        <v>1.35043462</v>
+      </c>
+      <c r="O40">
+        <v>0.270086924</v>
+      </c>
+      <c r="P40">
+        <v>1.080347696</v>
+      </c>
+      <c r="Q40">
+        <v>1.240347696</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1508416521895431</v>
+      </c>
+      <c r="T40">
+        <v>1.40343389153733</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.03656</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>23.67146822533491</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.107241865430336</v>
+      </c>
+      <c r="C41">
+        <v>2.130520947639012</v>
+      </c>
+      <c r="D41">
+        <v>3.103220947639012</v>
+      </c>
+      <c r="E41">
+        <v>-1.4723</v>
+      </c>
+      <c r="F41">
+        <v>1.3377</v>
+      </c>
+      <c r="G41">
+        <v>0.365</v>
+      </c>
+      <c r="H41">
+        <v>0.62</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.57</v>
+      </c>
+      <c r="K41">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L41">
+        <v>1.41</v>
+      </c>
+      <c r="M41">
+        <v>0.06113289000000001</v>
+      </c>
+      <c r="N41">
+        <v>1.34886711</v>
+      </c>
+      <c r="O41">
+        <v>0.2697734219999999</v>
+      </c>
+      <c r="P41">
+        <v>1.079093688</v>
+      </c>
+      <c r="Q41">
+        <v>1.239093688</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1524319105415343</v>
+      </c>
+      <c r="T41">
+        <v>1.423353469871549</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.03656</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>23.06450750160838</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1070691065031552</v>
+      </c>
+      <c r="C42">
+        <v>2.098281479136388</v>
+      </c>
+      <c r="D42">
+        <v>3.105281479136388</v>
+      </c>
+      <c r="E42">
+        <v>-1.438</v>
+      </c>
+      <c r="F42">
+        <v>1.372</v>
+      </c>
+      <c r="G42">
+        <v>0.365</v>
+      </c>
+      <c r="H42">
+        <v>0.62</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.57</v>
+      </c>
+      <c r="K42">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L42">
+        <v>1.41</v>
+      </c>
+      <c r="M42">
+        <v>0.06270040000000002</v>
+      </c>
+      <c r="N42">
+        <v>1.3472996</v>
+      </c>
+      <c r="O42">
+        <v>0.2694599199999999</v>
+      </c>
+      <c r="P42">
+        <v>1.07783968</v>
+      </c>
+      <c r="Q42">
+        <v>1.23783968</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1540751775052586</v>
+      </c>
+      <c r="T42">
+        <v>1.44393703415024</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.2</v>
+      </c>
+      <c r="W42">
+        <v>0.03656</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>22.48789481406817</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1068963475759744</v>
+      </c>
+      <c r="C43">
+        <v>2.06604474882817</v>
+      </c>
+      <c r="D43">
+        <v>3.10734474882817</v>
+      </c>
+      <c r="E43">
+        <v>-1.4037</v>
+      </c>
+      <c r="F43">
+        <v>1.4063</v>
+      </c>
+      <c r="G43">
+        <v>0.365</v>
+      </c>
+      <c r="H43">
+        <v>0.62</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.57</v>
+      </c>
+      <c r="K43">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L43">
+        <v>1.41</v>
+      </c>
+      <c r="M43">
+        <v>0.06426791000000001</v>
+      </c>
+      <c r="N43">
+        <v>1.34573209</v>
+      </c>
+      <c r="O43">
+        <v>0.2691464179999999</v>
+      </c>
+      <c r="P43">
+        <v>1.076585672</v>
+      </c>
+      <c r="Q43">
+        <v>1.236585672</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1557741484338549</v>
+      </c>
+      <c r="T43">
+        <v>1.465218346370583</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.2</v>
+      </c>
+      <c r="W43">
+        <v>0.03656</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>21.93940957470065</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1067235886487936</v>
+      </c>
+      <c r="C44">
+        <v>2.033810762176075</v>
+      </c>
+      <c r="D44">
+        <v>3.109410762176075</v>
+      </c>
+      <c r="E44">
+        <v>-1.3694</v>
+      </c>
+      <c r="F44">
+        <v>1.4406</v>
+      </c>
+      <c r="G44">
+        <v>0.365</v>
+      </c>
+      <c r="H44">
+        <v>0.62</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.57</v>
+      </c>
+      <c r="K44">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L44">
+        <v>1.41</v>
+      </c>
+      <c r="M44">
+        <v>0.06583542000000001</v>
+      </c>
+      <c r="N44">
+        <v>1.34416458</v>
+      </c>
+      <c r="O44">
+        <v>0.2688329159999999</v>
+      </c>
+      <c r="P44">
+        <v>1.075331664</v>
+      </c>
+      <c r="Q44">
+        <v>1.235331664</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1575317045668856</v>
+      </c>
+      <c r="T44">
+        <v>1.487233496943351</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.2</v>
+      </c>
+      <c r="W44">
+        <v>0.03656</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>21.41704268006492</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1065508297216129</v>
+      </c>
+      <c r="C45">
+        <v>2.001579524656354</v>
+      </c>
+      <c r="D45">
+        <v>3.111479524656354</v>
+      </c>
+      <c r="E45">
+        <v>-1.3351</v>
+      </c>
+      <c r="F45">
+        <v>1.4749</v>
+      </c>
+      <c r="G45">
+        <v>0.365</v>
+      </c>
+      <c r="H45">
+        <v>0.62</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.57</v>
+      </c>
+      <c r="K45">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L45">
+        <v>1.41</v>
+      </c>
+      <c r="M45">
+        <v>0.06740293000000001</v>
+      </c>
+      <c r="N45">
+        <v>1.34259707</v>
+      </c>
+      <c r="O45">
+        <v>0.2685194139999999</v>
+      </c>
+      <c r="P45">
+        <v>1.074077656</v>
+      </c>
+      <c r="Q45">
+        <v>1.234077656</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1593509293361629</v>
+      </c>
+      <c r="T45">
+        <v>1.510021108939725</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.2</v>
+      </c>
+      <c r="W45">
+        <v>0.03656</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>20.91897192006341</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1063780707944321</v>
+      </c>
+      <c r="C46">
+        <v>1.969351041759847</v>
+      </c>
+      <c r="D46">
+        <v>3.113551041759847</v>
+      </c>
+      <c r="E46">
+        <v>-1.3008</v>
+      </c>
+      <c r="F46">
+        <v>1.5092</v>
+      </c>
+      <c r="G46">
+        <v>0.365</v>
+      </c>
+      <c r="H46">
+        <v>0.62</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.57</v>
+      </c>
+      <c r="K46">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L46">
+        <v>1.41</v>
+      </c>
+      <c r="M46">
+        <v>0.06897044000000001</v>
+      </c>
+      <c r="N46">
+        <v>1.34102956</v>
+      </c>
+      <c r="O46">
+        <v>0.2682059119999999</v>
+      </c>
+      <c r="P46">
+        <v>1.072823648</v>
+      </c>
+      <c r="Q46">
+        <v>1.232823648</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1612351264186287</v>
+      </c>
+      <c r="T46">
+        <v>1.533622564221684</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.2</v>
+      </c>
+      <c r="W46">
+        <v>0.03656</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>20.44354074006197</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1062053118672513</v>
+      </c>
+      <c r="C47">
+        <v>1.93712531899202</v>
+      </c>
+      <c r="D47">
+        <v>3.11562531899202</v>
+      </c>
+      <c r="E47">
+        <v>-1.2665</v>
+      </c>
+      <c r="F47">
+        <v>1.5435</v>
+      </c>
+      <c r="G47">
+        <v>0.365</v>
+      </c>
+      <c r="H47">
+        <v>0.62</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.57</v>
+      </c>
+      <c r="K47">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L47">
+        <v>1.41</v>
+      </c>
+      <c r="M47">
+        <v>0.07053795000000002</v>
+      </c>
+      <c r="N47">
+        <v>1.33946205</v>
+      </c>
+      <c r="O47">
+        <v>0.2678924099999999</v>
+      </c>
+      <c r="P47">
+        <v>1.07156964</v>
+      </c>
+      <c r="Q47">
+        <v>1.23156964</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1631878397586388</v>
+      </c>
+      <c r="T47">
+        <v>1.558082254241169</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0.2</v>
+      </c>
+      <c r="W47">
+        <v>0.03656</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>19.98923983472726</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1060325529400706</v>
+      </c>
+      <c r="C48">
+        <v>1.904902361873022</v>
+      </c>
+      <c r="D48">
+        <v>3.117702361873022</v>
+      </c>
+      <c r="E48">
+        <v>-1.2322</v>
+      </c>
+      <c r="F48">
+        <v>1.5778</v>
+      </c>
+      <c r="G48">
+        <v>0.365</v>
+      </c>
+      <c r="H48">
+        <v>0.62</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.57</v>
+      </c>
+      <c r="K48">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L48">
+        <v>1.41</v>
+      </c>
+      <c r="M48">
+        <v>0.07210546000000001</v>
+      </c>
+      <c r="N48">
+        <v>1.33789454</v>
+      </c>
+      <c r="O48">
+        <v>0.2675789079999999</v>
+      </c>
+      <c r="P48">
+        <v>1.070315632</v>
+      </c>
+      <c r="Q48">
+        <v>1.230315632</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1652128758149455</v>
+      </c>
+      <c r="T48">
+        <v>1.583447858705819</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0.2</v>
+      </c>
+      <c r="W48">
+        <v>0.03656</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>19.55469114266797</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1058597940128898</v>
+      </c>
+      <c r="C49">
+        <v>1.872682175937733</v>
+      </c>
+      <c r="D49">
+        <v>3.119782175937733</v>
+      </c>
+      <c r="E49">
+        <v>-1.1979</v>
+      </c>
+      <c r="F49">
+        <v>1.6121</v>
+      </c>
+      <c r="G49">
+        <v>0.365</v>
+      </c>
+      <c r="H49">
+        <v>0.62</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.57</v>
+      </c>
+      <c r="K49">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L49">
+        <v>1.41</v>
+      </c>
+      <c r="M49">
+        <v>0.07367297000000002</v>
+      </c>
+      <c r="N49">
+        <v>1.33632703</v>
+      </c>
+      <c r="O49">
+        <v>0.2672654059999999</v>
+      </c>
+      <c r="P49">
+        <v>1.069061624</v>
+      </c>
+      <c r="Q49">
+        <v>1.229061624</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1673143283262071</v>
+      </c>
+      <c r="T49">
+        <v>1.609770655791777</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0.2</v>
+      </c>
+      <c r="W49">
+        <v>0.03656</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>19.13863388431333</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.105687035085709</v>
+      </c>
+      <c r="C50">
+        <v>1.84046476673581</v>
+      </c>
+      <c r="D50">
+        <v>3.121864766735811</v>
+      </c>
+      <c r="E50">
+        <v>-1.1636</v>
+      </c>
+      <c r="F50">
+        <v>1.6464</v>
+      </c>
+      <c r="G50">
+        <v>0.365</v>
+      </c>
+      <c r="H50">
+        <v>0.62</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.57</v>
+      </c>
+      <c r="K50">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L50">
+        <v>1.41</v>
+      </c>
+      <c r="M50">
+        <v>0.07524048000000001</v>
+      </c>
+      <c r="N50">
+        <v>1.33475952</v>
+      </c>
+      <c r="O50">
+        <v>0.266951904</v>
+      </c>
+      <c r="P50">
+        <v>1.067807616</v>
+      </c>
+      <c r="Q50">
+        <v>1.227807616</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1694966059340558</v>
+      </c>
+      <c r="T50">
+        <v>1.637105868150273</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0.2</v>
+      </c>
+      <c r="W50">
+        <v>0.03656</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>18.73991234505681</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1055142761585282</v>
+      </c>
+      <c r="C51">
+        <v>1.808250139831743</v>
+      </c>
+      <c r="D51">
+        <v>3.123950139831743</v>
+      </c>
+      <c r="E51">
+        <v>-1.1293</v>
+      </c>
+      <c r="F51">
+        <v>1.6807</v>
+      </c>
+      <c r="G51">
+        <v>0.365</v>
+      </c>
+      <c r="H51">
+        <v>0.62</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.57</v>
+      </c>
+      <c r="K51">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L51">
+        <v>1.41</v>
+      </c>
+      <c r="M51">
+        <v>0.07680799000000001</v>
+      </c>
+      <c r="N51">
+        <v>1.33319201</v>
+      </c>
+      <c r="O51">
+        <v>0.2666384019999999</v>
+      </c>
+      <c r="P51">
+        <v>1.066553608</v>
+      </c>
+      <c r="Q51">
+        <v>1.226553608</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1717644630559377</v>
+      </c>
+      <c r="T51">
+        <v>1.665513049620865</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0.2</v>
+      </c>
+      <c r="W51">
+        <v>0.03656</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>18.35746515434136</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1053415172313475</v>
+      </c>
+      <c r="C52">
+        <v>1.776038300804892</v>
+      </c>
+      <c r="D52">
+        <v>3.126038300804892</v>
+      </c>
+      <c r="E52">
+        <v>-1.095</v>
+      </c>
+      <c r="F52">
+        <v>1.715</v>
+      </c>
+      <c r="G52">
+        <v>0.365</v>
+      </c>
+      <c r="H52">
+        <v>0.62</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.57</v>
+      </c>
+      <c r="K52">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L52">
+        <v>1.41</v>
+      </c>
+      <c r="M52">
+        <v>0.07837550000000001</v>
+      </c>
+      <c r="N52">
+        <v>1.3316245</v>
+      </c>
+      <c r="O52">
+        <v>0.2663248999999999</v>
+      </c>
+      <c r="P52">
+        <v>1.0652996</v>
+      </c>
+      <c r="Q52">
+        <v>1.2252996</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1741230344626949</v>
+      </c>
+      <c r="T52">
+        <v>1.695056518350282</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0.2</v>
+      </c>
+      <c r="W52">
+        <v>0.03656</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>17.99031585125453</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1051687583041667</v>
+      </c>
+      <c r="C53">
+        <v>1.743829255249554</v>
+      </c>
+      <c r="D53">
+        <v>3.128129255249554</v>
+      </c>
+      <c r="E53">
+        <v>-1.0607</v>
+      </c>
+      <c r="F53">
+        <v>1.7493</v>
+      </c>
+      <c r="G53">
+        <v>0.365</v>
+      </c>
+      <c r="H53">
+        <v>0.62</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.57</v>
+      </c>
+      <c r="K53">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L53">
+        <v>1.41</v>
+      </c>
+      <c r="M53">
+        <v>0.07994301000000001</v>
+      </c>
+      <c r="N53">
+        <v>1.33005699</v>
+      </c>
+      <c r="O53">
+        <v>0.2660113979999999</v>
+      </c>
+      <c r="P53">
+        <v>1.064045592</v>
+      </c>
+      <c r="Q53">
+        <v>1.224045592</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1765778740901361</v>
+      </c>
+      <c r="T53">
+        <v>1.725805842946206</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0.2</v>
+      </c>
+      <c r="W53">
+        <v>0.03656</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>17.63756456005347</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1049959993769859</v>
+      </c>
+      <c r="C54">
+        <v>1.711623008774997</v>
+      </c>
+      <c r="D54">
+        <v>3.130223008774997</v>
+      </c>
+      <c r="E54">
+        <v>-1.0264</v>
+      </c>
+      <c r="F54">
+        <v>1.7836</v>
+      </c>
+      <c r="G54">
+        <v>0.365</v>
+      </c>
+      <c r="H54">
+        <v>0.62</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.57</v>
+      </c>
+      <c r="K54">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L54">
+        <v>1.41</v>
+      </c>
+      <c r="M54">
+        <v>0.08151052000000002</v>
+      </c>
+      <c r="N54">
+        <v>1.32848948</v>
+      </c>
+      <c r="O54">
+        <v>0.2656978959999999</v>
+      </c>
+      <c r="P54">
+        <v>1.062791584</v>
+      </c>
+      <c r="Q54">
+        <v>1.222791584</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.179134998702054</v>
+      </c>
+      <c r="T54">
+        <v>1.757836389400293</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0.2</v>
+      </c>
+      <c r="W54">
+        <v>0.03656</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>17.29838062620628</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1048232404498051</v>
+      </c>
+      <c r="C55">
+        <v>1.679419567005519</v>
+      </c>
+      <c r="D55">
+        <v>3.132319567005519</v>
+      </c>
+      <c r="E55">
+        <v>-0.9921</v>
+      </c>
+      <c r="F55">
+        <v>1.8179</v>
+      </c>
+      <c r="G55">
+        <v>0.365</v>
+      </c>
+      <c r="H55">
+        <v>0.62</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.57</v>
+      </c>
+      <c r="K55">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L55">
+        <v>1.41</v>
+      </c>
+      <c r="M55">
+        <v>0.08307803000000001</v>
+      </c>
+      <c r="N55">
+        <v>1.32692197</v>
+      </c>
+      <c r="O55">
+        <v>0.2653843939999999</v>
+      </c>
+      <c r="P55">
+        <v>1.061537576</v>
+      </c>
+      <c r="Q55">
+        <v>1.221537576</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.181800937127245</v>
+      </c>
+      <c r="T55">
+        <v>1.79122993783115</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0.2</v>
+      </c>
+      <c r="W55">
+        <v>0.03656</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>16.97199608608918</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1046504815226244</v>
+      </c>
+      <c r="C56">
+        <v>1.647218935580497</v>
+      </c>
+      <c r="D56">
+        <v>3.134418935580497</v>
+      </c>
+      <c r="E56">
+        <v>-0.9577999999999998</v>
+      </c>
+      <c r="F56">
+        <v>1.8522</v>
+      </c>
+      <c r="G56">
+        <v>0.365</v>
+      </c>
+      <c r="H56">
+        <v>0.62</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.57</v>
+      </c>
+      <c r="K56">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L56">
+        <v>1.41</v>
+      </c>
+      <c r="M56">
+        <v>0.08464554000000002</v>
+      </c>
+      <c r="N56">
+        <v>1.32535446</v>
+      </c>
+      <c r="O56">
+        <v>0.2650708919999999</v>
+      </c>
+      <c r="P56">
+        <v>1.060283568</v>
+      </c>
+      <c r="Q56">
+        <v>1.220283568</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1845827859187486</v>
+      </c>
+      <c r="T56">
+        <v>1.826075379672043</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0.2</v>
+      </c>
+      <c r="W56">
+        <v>0.03656</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>16.65769986227271</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1044777225954436</v>
+      </c>
+      <c r="C57">
+        <v>1.615021120154436</v>
+      </c>
+      <c r="D57">
+        <v>3.136521120154436</v>
+      </c>
+      <c r="E57">
+        <v>-0.9234999999999998</v>
+      </c>
+      <c r="F57">
+        <v>1.8865</v>
+      </c>
+      <c r="G57">
+        <v>0.365</v>
+      </c>
+      <c r="H57">
+        <v>0.62</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.57</v>
+      </c>
+      <c r="K57">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L57">
+        <v>1.41</v>
+      </c>
+      <c r="M57">
+        <v>0.08621305000000003</v>
+      </c>
+      <c r="N57">
+        <v>1.32378695</v>
+      </c>
+      <c r="O57">
+        <v>0.2647573899999999</v>
+      </c>
+      <c r="P57">
+        <v>1.05902956</v>
+      </c>
+      <c r="Q57">
+        <v>1.21902956</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1874882724343191</v>
+      </c>
+      <c r="T57">
+        <v>1.862469507816977</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0.2</v>
+      </c>
+      <c r="W57">
+        <v>0.03656</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>16.35483259204958</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1043049636682628</v>
+      </c>
+      <c r="C58">
+        <v>1.582826126397022</v>
+      </c>
+      <c r="D58">
+        <v>3.138626126397023</v>
+      </c>
+      <c r="E58">
+        <v>-0.8891999999999998</v>
+      </c>
+      <c r="F58">
+        <v>1.9208</v>
+      </c>
+      <c r="G58">
+        <v>0.365</v>
+      </c>
+      <c r="H58">
+        <v>0.62</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.57</v>
+      </c>
+      <c r="K58">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L58">
+        <v>1.41</v>
+      </c>
+      <c r="M58">
+        <v>0.08778056000000002</v>
+      </c>
+      <c r="N58">
+        <v>1.32221944</v>
+      </c>
+      <c r="O58">
+        <v>0.2644438879999999</v>
+      </c>
+      <c r="P58">
+        <v>1.057775552</v>
+      </c>
+      <c r="Q58">
+        <v>1.217775552</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1905258265187791</v>
+      </c>
+      <c r="T58">
+        <v>1.900517914513953</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0.2</v>
+      </c>
+      <c r="W58">
+        <v>0.03656</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>16.06278201004869</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.104132204741082</v>
+      </c>
+      <c r="C59">
+        <v>1.550633959993168</v>
+      </c>
+      <c r="D59">
+        <v>3.140733959993169</v>
+      </c>
+      <c r="E59">
+        <v>-0.8548999999999998</v>
+      </c>
+      <c r="F59">
+        <v>1.9551</v>
+      </c>
+      <c r="G59">
+        <v>0.365</v>
+      </c>
+      <c r="H59">
+        <v>0.62</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.57</v>
+      </c>
+      <c r="K59">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L59">
+        <v>1.41</v>
+      </c>
+      <c r="M59">
+        <v>0.08934807000000002</v>
+      </c>
+      <c r="N59">
+        <v>1.32065193</v>
+      </c>
+      <c r="O59">
+        <v>0.2641303859999999</v>
+      </c>
+      <c r="P59">
+        <v>1.056521544</v>
+      </c>
+      <c r="Q59">
+        <v>1.216521544</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1937046621885629</v>
+      </c>
+      <c r="T59">
+        <v>1.940336014545672</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0.2</v>
+      </c>
+      <c r="W59">
+        <v>0.03656</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>15.78097881688994</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1039594458139013</v>
+      </c>
+      <c r="C60">
+        <v>1.518444626643075</v>
+      </c>
+      <c r="D60">
+        <v>3.142844626643075</v>
+      </c>
+      <c r="E60">
+        <v>-0.8206</v>
+      </c>
+      <c r="F60">
+        <v>1.9894</v>
+      </c>
+      <c r="G60">
+        <v>0.365</v>
+      </c>
+      <c r="H60">
+        <v>0.62</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.57</v>
+      </c>
+      <c r="K60">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L60">
+        <v>1.41</v>
+      </c>
+      <c r="M60">
+        <v>0.09091558000000001</v>
+      </c>
+      <c r="N60">
+        <v>1.31908442</v>
+      </c>
+      <c r="O60">
+        <v>0.2638168839999999</v>
+      </c>
+      <c r="P60">
+        <v>1.055267536</v>
+      </c>
+      <c r="Q60">
+        <v>1.215267536</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1970348709854792</v>
+      </c>
+      <c r="T60">
+        <v>1.982050214578901</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0.2</v>
+      </c>
+      <c r="W60">
+        <v>0.03656</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>15.50889297521942</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1037866868867205</v>
+      </c>
+      <c r="C61">
+        <v>1.486258132062269</v>
+      </c>
+      <c r="D61">
+        <v>3.144958132062269</v>
+      </c>
+      <c r="E61">
+        <v>-0.7863000000000002</v>
+      </c>
+      <c r="F61">
+        <v>2.0237</v>
+      </c>
+      <c r="G61">
+        <v>0.365</v>
+      </c>
+      <c r="H61">
+        <v>0.62</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.57</v>
+      </c>
+      <c r="K61">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L61">
+        <v>1.41</v>
+      </c>
+      <c r="M61">
+        <v>0.09248309</v>
+      </c>
+      <c r="N61">
+        <v>1.31751691</v>
+      </c>
+      <c r="O61">
+        <v>0.263503382</v>
+      </c>
+      <c r="P61">
+        <v>1.054013528</v>
+      </c>
+      <c r="Q61">
+        <v>1.214013528</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2005275289920012</v>
+      </c>
+      <c r="T61">
+        <v>2.025799253638142</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0.2</v>
+      </c>
+      <c r="W61">
+        <v>0.03656</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>15.2460303824191</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1036139279595397</v>
+      </c>
+      <c r="C62">
+        <v>1.454074481981667</v>
+      </c>
+      <c r="D62">
+        <v>3.147074481981667</v>
+      </c>
+      <c r="E62">
+        <v>-0.7520000000000002</v>
+      </c>
+      <c r="F62">
+        <v>2.058</v>
+      </c>
+      <c r="G62">
+        <v>0.365</v>
+      </c>
+      <c r="H62">
+        <v>0.62</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.57</v>
+      </c>
+      <c r="K62">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L62">
+        <v>1.41</v>
+      </c>
+      <c r="M62">
+        <v>0.0940506</v>
+      </c>
+      <c r="N62">
+        <v>1.3159494</v>
+      </c>
+      <c r="O62">
+        <v>0.2631898799999999</v>
+      </c>
+      <c r="P62">
+        <v>1.05275952</v>
+      </c>
+      <c r="Q62">
+        <v>1.21275952</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2041948198988494</v>
+      </c>
+      <c r="T62">
+        <v>2.071735744650345</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0.2</v>
+      </c>
+      <c r="W62">
+        <v>0.03656</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>14.99192987604545</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.103441169032359</v>
+      </c>
+      <c r="C63">
+        <v>1.42189368214762</v>
+      </c>
+      <c r="D63">
+        <v>3.14919368214762</v>
+      </c>
+      <c r="E63">
+        <v>-0.7176999999999998</v>
+      </c>
+      <c r="F63">
+        <v>2.0923</v>
+      </c>
+      <c r="G63">
+        <v>0.365</v>
+      </c>
+      <c r="H63">
+        <v>0.62</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.57</v>
+      </c>
+      <c r="K63">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L63">
+        <v>1.41</v>
+      </c>
+      <c r="M63">
+        <v>0.09561811000000002</v>
+      </c>
+      <c r="N63">
+        <v>1.31438189</v>
+      </c>
+      <c r="O63">
+        <v>0.2628763779999999</v>
+      </c>
+      <c r="P63">
+        <v>1.051505512</v>
+      </c>
+      <c r="Q63">
+        <v>1.211505512</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2080501770060486</v>
+      </c>
+      <c r="T63">
+        <v>2.120027953150353</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0.2</v>
+      </c>
+      <c r="W63">
+        <v>0.03656</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>14.74616053381519</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1032684101051782</v>
+      </c>
+      <c r="C64">
+        <v>1.389715738321967</v>
+      </c>
+      <c r="D64">
+        <v>3.151315738321968</v>
+      </c>
+      <c r="E64">
+        <v>-0.6833999999999998</v>
+      </c>
+      <c r="F64">
+        <v>2.1266</v>
+      </c>
+      <c r="G64">
+        <v>0.365</v>
+      </c>
+      <c r="H64">
+        <v>0.62</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.57</v>
+      </c>
+      <c r="K64">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L64">
+        <v>1.41</v>
+      </c>
+      <c r="M64">
+        <v>0.09718562000000003</v>
+      </c>
+      <c r="N64">
+        <v>1.31281438</v>
+      </c>
+      <c r="O64">
+        <v>0.2625628759999999</v>
+      </c>
+      <c r="P64">
+        <v>1.050251504</v>
+      </c>
+      <c r="Q64">
+        <v>1.210251504</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2121084476452058</v>
+      </c>
+      <c r="T64">
+        <v>2.170861856834572</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0.2</v>
+      </c>
+      <c r="W64">
+        <v>0.03656</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>14.50831923488269</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1030956511779974</v>
+      </c>
+      <c r="C65">
+        <v>1.357540656282092</v>
+      </c>
+      <c r="D65">
+        <v>3.153440656282092</v>
+      </c>
+      <c r="E65">
+        <v>-0.6490999999999998</v>
+      </c>
+      <c r="F65">
+        <v>2.1609</v>
+      </c>
+      <c r="G65">
+        <v>0.365</v>
+      </c>
+      <c r="H65">
+        <v>0.62</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.57</v>
+      </c>
+      <c r="K65">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L65">
+        <v>1.41</v>
+      </c>
+      <c r="M65">
+        <v>0.09875313000000002</v>
+      </c>
+      <c r="N65">
+        <v>1.31124687</v>
+      </c>
+      <c r="O65">
+        <v>0.2622493739999999</v>
+      </c>
+      <c r="P65">
+        <v>1.048997496</v>
+      </c>
+      <c r="Q65">
+        <v>1.208997496</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2163860842648579</v>
+      </c>
+      <c r="T65">
+        <v>2.224443539096316</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0.2</v>
+      </c>
+      <c r="W65">
+        <v>0.03656</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>14.27802845337661</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1029228922508166</v>
+      </c>
+      <c r="C66">
+        <v>1.325368441820964</v>
+      </c>
+      <c r="D66">
+        <v>3.155568441820964</v>
+      </c>
+      <c r="E66">
+        <v>-0.6147999999999998</v>
+      </c>
+      <c r="F66">
+        <v>2.1952</v>
+      </c>
+      <c r="G66">
+        <v>0.365</v>
+      </c>
+      <c r="H66">
+        <v>0.62</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.57</v>
+      </c>
+      <c r="K66">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L66">
+        <v>1.41</v>
+      </c>
+      <c r="M66">
+        <v>0.10032064</v>
+      </c>
+      <c r="N66">
+        <v>1.30967936</v>
+      </c>
+      <c r="O66">
+        <v>0.2619358719999999</v>
+      </c>
+      <c r="P66">
+        <v>1.047743488</v>
+      </c>
+      <c r="Q66">
+        <v>1.207743488</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2209013673633796</v>
+      </c>
+      <c r="T66">
+        <v>2.281001981483713</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0.2</v>
+      </c>
+      <c r="W66">
+        <v>0.03656</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>14.0549342587926</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1027501333236359</v>
+      </c>
+      <c r="C67">
+        <v>1.293199100747206</v>
+      </c>
+      <c r="D67">
+        <v>3.157699100747207</v>
+      </c>
+      <c r="E67">
+        <v>-0.5804999999999998</v>
+      </c>
+      <c r="F67">
+        <v>2.2295</v>
+      </c>
+      <c r="G67">
+        <v>0.365</v>
+      </c>
+      <c r="H67">
+        <v>0.62</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.57</v>
+      </c>
+      <c r="K67">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L67">
+        <v>1.41</v>
+      </c>
+      <c r="M67">
+        <v>0.10188815</v>
+      </c>
+      <c r="N67">
+        <v>1.30811185</v>
+      </c>
+      <c r="O67">
+        <v>0.2616223699999999</v>
+      </c>
+      <c r="P67">
+        <v>1.04648948</v>
+      </c>
+      <c r="Q67">
+        <v>1.20648948</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2256746666389596</v>
+      </c>
+      <c r="T67">
+        <v>2.340792334864676</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0.2</v>
+      </c>
+      <c r="W67">
+        <v>0.03656</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>13.83870450096503</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1025773743964551</v>
+      </c>
+      <c r="C68">
+        <v>1.261032638885136</v>
+      </c>
+      <c r="D68">
+        <v>3.159832638885136</v>
+      </c>
+      <c r="E68">
+        <v>-0.5461999999999998</v>
+      </c>
+      <c r="F68">
+        <v>2.2638</v>
+      </c>
+      <c r="G68">
+        <v>0.365</v>
+      </c>
+      <c r="H68">
+        <v>0.62</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.57</v>
+      </c>
+      <c r="K68">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L68">
+        <v>1.41</v>
+      </c>
+      <c r="M68">
+        <v>0.10345566</v>
+      </c>
+      <c r="N68">
+        <v>1.30654434</v>
+      </c>
+      <c r="O68">
+        <v>0.2613088679999999</v>
+      </c>
+      <c r="P68">
+        <v>1.045235472</v>
+      </c>
+      <c r="Q68">
+        <v>1.205235472</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.230728748224868</v>
+      </c>
+      <c r="T68">
+        <v>2.404099767856283</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0.2</v>
+      </c>
+      <c r="W68">
+        <v>0.03656</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>13.62902716004131</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1024046154692743</v>
+      </c>
+      <c r="C69">
+        <v>1.228869062074823</v>
+      </c>
+      <c r="D69">
+        <v>3.161969062074823</v>
+      </c>
+      <c r="E69">
+        <v>-0.5118999999999998</v>
+      </c>
+      <c r="F69">
+        <v>2.2981</v>
+      </c>
+      <c r="G69">
+        <v>0.365</v>
+      </c>
+      <c r="H69">
+        <v>0.62</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.57</v>
+      </c>
+      <c r="K69">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L69">
+        <v>1.41</v>
+      </c>
+      <c r="M69">
+        <v>0.10502317</v>
+      </c>
+      <c r="N69">
+        <v>1.30497683</v>
+      </c>
+      <c r="O69">
+        <v>0.260995366</v>
+      </c>
+      <c r="P69">
+        <v>1.043981464</v>
+      </c>
+      <c r="Q69">
+        <v>1.203981464</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2360891377856798</v>
+      </c>
+      <c r="T69">
+        <v>2.471244014968594</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0.2</v>
+      </c>
+      <c r="W69">
+        <v>0.03656</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>13.4256088442198</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1022318565420935</v>
+      </c>
+      <c r="C70">
+        <v>1.196708376172142</v>
+      </c>
+      <c r="D70">
+        <v>3.164108376172142</v>
+      </c>
+      <c r="E70">
+        <v>-0.4775999999999998</v>
+      </c>
+      <c r="F70">
+        <v>2.3324</v>
+      </c>
+      <c r="G70">
+        <v>0.365</v>
+      </c>
+      <c r="H70">
+        <v>0.62</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.57</v>
+      </c>
+      <c r="K70">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L70">
+        <v>1.41</v>
+      </c>
+      <c r="M70">
+        <v>0.10659068</v>
+      </c>
+      <c r="N70">
+        <v>1.30340932</v>
+      </c>
+      <c r="O70">
+        <v>0.2606818639999999</v>
+      </c>
+      <c r="P70">
+        <v>1.042727456</v>
+      </c>
+      <c r="Q70">
+        <v>1.202727456</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2417845516940424</v>
+      </c>
+      <c r="T70">
+        <v>2.542584777525423</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0.2</v>
+      </c>
+      <c r="W70">
+        <v>0.03656</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>13.2281734200401</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1020590976149128</v>
+      </c>
+      <c r="C71">
+        <v>1.164550587048828</v>
+      </c>
+      <c r="D71">
+        <v>3.166250587048828</v>
+      </c>
+      <c r="E71">
+        <v>-0.4432999999999998</v>
+      </c>
+      <c r="F71">
+        <v>2.3667</v>
+      </c>
+      <c r="G71">
+        <v>0.365</v>
+      </c>
+      <c r="H71">
+        <v>0.62</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.57</v>
+      </c>
+      <c r="K71">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L71">
+        <v>1.41</v>
+      </c>
+      <c r="M71">
+        <v>0.10815819</v>
+      </c>
+      <c r="N71">
+        <v>1.30184181</v>
+      </c>
+      <c r="O71">
+        <v>0.260368362</v>
+      </c>
+      <c r="P71">
+        <v>1.041473448</v>
+      </c>
+      <c r="Q71">
+        <v>1.201473448</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.247847411661009</v>
+      </c>
+      <c r="T71">
+        <v>2.61852816992463</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0.2</v>
+      </c>
+      <c r="W71">
+        <v>0.03656</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>13.03646076177865</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.102782338687732</v>
+      </c>
+      <c r="C72">
+        <v>1.121301689524983</v>
+      </c>
+      <c r="D72">
+        <v>3.157301689524983</v>
+      </c>
+      <c r="E72">
+        <v>-0.4089999999999998</v>
+      </c>
+      <c r="F72">
+        <v>2.401</v>
+      </c>
+      <c r="G72">
+        <v>0.365</v>
+      </c>
+      <c r="H72">
+        <v>0.62</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.57</v>
+      </c>
+      <c r="K72">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L72">
+        <v>1.41</v>
+      </c>
+      <c r="M72">
+        <v>0.1135673</v>
+      </c>
+      <c r="N72">
+        <v>1.2964327</v>
+      </c>
+      <c r="O72">
+        <v>0.25928654</v>
+      </c>
+      <c r="P72">
+        <v>1.03714616</v>
+      </c>
+      <c r="Q72">
+        <v>1.19714616</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2543144622924401</v>
+      </c>
+      <c r="T72">
+        <v>2.69953445515045</v>
+      </c>
+      <c r="U72">
+        <v>0.0473</v>
+      </c>
+      <c r="V72">
+        <v>0.2</v>
+      </c>
+      <c r="W72">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>12.41554567203764</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1026223797605512</v>
+      </c>
+      <c r="C73">
+        <v>1.088976553997662</v>
+      </c>
+      <c r="D73">
+        <v>3.159276553997661</v>
+      </c>
+      <c r="E73">
+        <v>-0.3747000000000003</v>
+      </c>
+      <c r="F73">
+        <v>2.4353</v>
+      </c>
+      <c r="G73">
+        <v>0.365</v>
+      </c>
+      <c r="H73">
+        <v>0.62</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.57</v>
+      </c>
+      <c r="K73">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L73">
+        <v>1.41</v>
+      </c>
+      <c r="M73">
+        <v>0.11518969</v>
+      </c>
+      <c r="N73">
+        <v>1.29481031</v>
+      </c>
+      <c r="O73">
+        <v>0.2589620619999999</v>
+      </c>
+      <c r="P73">
+        <v>1.035848248</v>
+      </c>
+      <c r="Q73">
+        <v>1.195848248</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2612275164156939</v>
+      </c>
+      <c r="T73">
+        <v>2.786127380736671</v>
+      </c>
+      <c r="U73">
+        <v>0.0473</v>
+      </c>
+      <c r="V73">
+        <v>0.2</v>
+      </c>
+      <c r="W73">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>12.2406788315864</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1024624208333705</v>
+      </c>
+      <c r="C74">
+        <v>1.056653890537356</v>
+      </c>
+      <c r="D74">
+        <v>3.161253890537356</v>
+      </c>
+      <c r="E74">
+        <v>-0.3403999999999998</v>
+      </c>
+      <c r="F74">
+        <v>2.4696</v>
+      </c>
+      <c r="G74">
+        <v>0.365</v>
+      </c>
+      <c r="H74">
+        <v>0.62</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.57</v>
+      </c>
+      <c r="K74">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L74">
+        <v>1.41</v>
+      </c>
+      <c r="M74">
+        <v>0.11681208</v>
+      </c>
+      <c r="N74">
+        <v>1.29318792</v>
+      </c>
+      <c r="O74">
+        <v>0.2586375839999999</v>
+      </c>
+      <c r="P74">
+        <v>1.034550336</v>
+      </c>
+      <c r="Q74">
+        <v>1.194550336</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2686343601191802</v>
+      </c>
+      <c r="T74">
+        <v>2.878905515293336</v>
+      </c>
+      <c r="U74">
+        <v>0.0473</v>
+      </c>
+      <c r="V74">
+        <v>0.2</v>
+      </c>
+      <c r="W74">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>12.07066940336992</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1023024619061897</v>
+      </c>
+      <c r="C75">
+        <v>1.024333703788647</v>
+      </c>
+      <c r="D75">
+        <v>3.163233703788647</v>
+      </c>
+      <c r="E75">
+        <v>-0.3060999999999998</v>
+      </c>
+      <c r="F75">
+        <v>2.5039</v>
+      </c>
+      <c r="G75">
+        <v>0.365</v>
+      </c>
+      <c r="H75">
+        <v>0.62</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.57</v>
+      </c>
+      <c r="K75">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L75">
+        <v>1.41</v>
+      </c>
+      <c r="M75">
+        <v>0.11843447</v>
+      </c>
+      <c r="N75">
+        <v>1.29156553</v>
+      </c>
+      <c r="O75">
+        <v>0.258313106</v>
+      </c>
+      <c r="P75">
+        <v>1.033252424</v>
+      </c>
+      <c r="Q75">
+        <v>1.193252424</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2765898589118136</v>
+      </c>
+      <c r="T75">
+        <v>2.978556104261607</v>
+      </c>
+      <c r="U75">
+        <v>0.0473</v>
+      </c>
+      <c r="V75">
+        <v>0.2</v>
+      </c>
+      <c r="W75">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>11.90531776770732</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1021425029790089</v>
+      </c>
+      <c r="C76">
+        <v>0.9920159984077537</v>
+      </c>
+      <c r="D76">
+        <v>3.165215998407754</v>
+      </c>
+      <c r="E76">
+        <v>-0.2717999999999998</v>
+      </c>
+      <c r="F76">
+        <v>2.5382</v>
+      </c>
+      <c r="G76">
+        <v>0.365</v>
+      </c>
+      <c r="H76">
+        <v>0.62</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.57</v>
+      </c>
+      <c r="K76">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L76">
+        <v>1.41</v>
+      </c>
+      <c r="M76">
+        <v>0.12005686</v>
+      </c>
+      <c r="N76">
+        <v>1.28994314</v>
+      </c>
+      <c r="O76">
+        <v>0.2579886279999999</v>
+      </c>
+      <c r="P76">
+        <v>1.031954512</v>
+      </c>
+      <c r="Q76">
+        <v>1.191954512</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2851573191500343</v>
+      </c>
+      <c r="T76">
+        <v>3.085872123150514</v>
+      </c>
+      <c r="U76">
+        <v>0.0473</v>
+      </c>
+      <c r="V76">
+        <v>0.2</v>
+      </c>
+      <c r="W76">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>11.74443509517074</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1019825440518282</v>
+      </c>
+      <c r="C77">
+        <v>0.9597007790625782</v>
+      </c>
+      <c r="D77">
+        <v>3.167200779062579</v>
+      </c>
+      <c r="E77">
+        <v>-0.2374999999999998</v>
+      </c>
+      <c r="F77">
+        <v>2.5725</v>
+      </c>
+      <c r="G77">
+        <v>0.365</v>
+      </c>
+      <c r="H77">
+        <v>0.62</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.57</v>
+      </c>
+      <c r="K77">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L77">
+        <v>1.41</v>
+      </c>
+      <c r="M77">
+        <v>0.12167925</v>
+      </c>
+      <c r="N77">
+        <v>1.28832075</v>
+      </c>
+      <c r="O77">
+        <v>0.2576641499999999</v>
+      </c>
+      <c r="P77">
+        <v>1.0306566</v>
+      </c>
+      <c r="Q77">
+        <v>1.1906566</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2944101762073126</v>
+      </c>
+      <c r="T77">
+        <v>3.201773423550534</v>
+      </c>
+      <c r="U77">
+        <v>0.0473</v>
+      </c>
+      <c r="V77">
+        <v>0.2</v>
+      </c>
+      <c r="W77">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>11.58784262723513</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1018225851246474</v>
+      </c>
+      <c r="C78">
+        <v>0.9273880504327354</v>
+      </c>
+      <c r="D78">
+        <v>3.169188050432736</v>
+      </c>
+      <c r="E78">
+        <v>-0.2031999999999998</v>
+      </c>
+      <c r="F78">
+        <v>2.6068</v>
+      </c>
+      <c r="G78">
+        <v>0.365</v>
+      </c>
+      <c r="H78">
+        <v>0.62</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.57</v>
+      </c>
+      <c r="K78">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L78">
+        <v>1.41</v>
+      </c>
+      <c r="M78">
+        <v>0.12330164</v>
+      </c>
+      <c r="N78">
+        <v>1.28669836</v>
+      </c>
+      <c r="O78">
+        <v>0.2573396719999999</v>
+      </c>
+      <c r="P78">
+        <v>1.029358688</v>
+      </c>
+      <c r="Q78">
+        <v>1.189358688</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3044341046860308</v>
+      </c>
+      <c r="T78">
+        <v>3.327333165650554</v>
+      </c>
+      <c r="U78">
+        <v>0.0473</v>
+      </c>
+      <c r="V78">
+        <v>0.2</v>
+      </c>
+      <c r="W78">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>11.43537101371887</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1016626261974666</v>
+      </c>
+      <c r="C79">
+        <v>0.8950778172095943</v>
+      </c>
+      <c r="D79">
+        <v>3.171177817209594</v>
+      </c>
+      <c r="E79">
+        <v>-0.1688999999999998</v>
+      </c>
+      <c r="F79">
+        <v>2.6411</v>
+      </c>
+      <c r="G79">
+        <v>0.365</v>
+      </c>
+      <c r="H79">
+        <v>0.62</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.57</v>
+      </c>
+      <c r="K79">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L79">
+        <v>1.41</v>
+      </c>
+      <c r="M79">
+        <v>0.12492403</v>
+      </c>
+      <c r="N79">
+        <v>1.28507597</v>
+      </c>
+      <c r="O79">
+        <v>0.2570151939999999</v>
+      </c>
+      <c r="P79">
+        <v>1.028060776</v>
+      </c>
+      <c r="Q79">
+        <v>1.188060776</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3153296791194201</v>
+      </c>
+      <c r="T79">
+        <v>3.463811146194056</v>
+      </c>
+      <c r="U79">
+        <v>0.0473</v>
+      </c>
+      <c r="V79">
+        <v>0.2</v>
+      </c>
+      <c r="W79">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>11.28685970185239</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1015026672702858</v>
+      </c>
+      <c r="C80">
+        <v>0.8627700840963111</v>
+      </c>
+      <c r="D80">
+        <v>3.173170084096311</v>
+      </c>
+      <c r="E80">
+        <v>-0.1345999999999998</v>
+      </c>
+      <c r="F80">
+        <v>2.6754</v>
+      </c>
+      <c r="G80">
+        <v>0.365</v>
+      </c>
+      <c r="H80">
+        <v>0.62</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.57</v>
+      </c>
+      <c r="K80">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L80">
+        <v>1.41</v>
+      </c>
+      <c r="M80">
+        <v>0.12654642</v>
+      </c>
+      <c r="N80">
+        <v>1.28345358</v>
+      </c>
+      <c r="O80">
+        <v>0.2566907159999999</v>
+      </c>
+      <c r="P80">
+        <v>1.026762864</v>
+      </c>
+      <c r="Q80">
+        <v>1.186762864</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3272157603194811</v>
+      </c>
+      <c r="T80">
+        <v>3.612696215877875</v>
+      </c>
+      <c r="U80">
+        <v>0.0473</v>
+      </c>
+      <c r="V80">
+        <v>0.2</v>
+      </c>
+      <c r="W80">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>11.14215637234147</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1013427083431051</v>
+      </c>
+      <c r="C81">
+        <v>0.8304648558078696</v>
+      </c>
+      <c r="D81">
+        <v>3.17516485580787</v>
+      </c>
+      <c r="E81">
+        <v>-0.1002999999999998</v>
+      </c>
+      <c r="F81">
+        <v>2.7097</v>
+      </c>
+      <c r="G81">
+        <v>0.365</v>
+      </c>
+      <c r="H81">
+        <v>0.62</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.57</v>
+      </c>
+      <c r="K81">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L81">
+        <v>1.41</v>
+      </c>
+      <c r="M81">
+        <v>0.12816881</v>
+      </c>
+      <c r="N81">
+        <v>1.28183119</v>
+      </c>
+      <c r="O81">
+        <v>0.2563662379999999</v>
+      </c>
+      <c r="P81">
+        <v>1.025464952</v>
+      </c>
+      <c r="Q81">
+        <v>1.185464952</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3402338492528813</v>
+      </c>
+      <c r="T81">
+        <v>3.775760816007772</v>
+      </c>
+      <c r="U81">
+        <v>0.0473</v>
+      </c>
+      <c r="V81">
+        <v>0.2</v>
+      </c>
+      <c r="W81">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>11.0011164182612</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1011827494159243</v>
+      </c>
+      <c r="C82">
+        <v>0.798162137071118</v>
+      </c>
+      <c r="D82">
+        <v>3.177162137071118</v>
+      </c>
+      <c r="E82">
+        <v>-0.06599999999999984</v>
+      </c>
+      <c r="F82">
+        <v>2.744</v>
+      </c>
+      <c r="G82">
+        <v>0.365</v>
+      </c>
+      <c r="H82">
+        <v>0.62</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.57</v>
+      </c>
+      <c r="K82">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L82">
+        <v>1.41</v>
+      </c>
+      <c r="M82">
+        <v>0.1297912</v>
+      </c>
+      <c r="N82">
+        <v>1.2802088</v>
+      </c>
+      <c r="O82">
+        <v>0.2560417599999999</v>
+      </c>
+      <c r="P82">
+        <v>1.02416704</v>
+      </c>
+      <c r="Q82">
+        <v>1.18416704</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3545537470796216</v>
+      </c>
+      <c r="T82">
+        <v>3.95513187615066</v>
+      </c>
+      <c r="U82">
+        <v>0.0473</v>
+      </c>
+      <c r="V82">
+        <v>0.2</v>
+      </c>
+      <c r="W82">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>10.86360246303293</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1010227904887435</v>
+      </c>
+      <c r="C83">
+        <v>0.7658619326248028</v>
+      </c>
+      <c r="D83">
+        <v>3.179161932624803</v>
+      </c>
+      <c r="E83">
+        <v>-0.03169999999999984</v>
+      </c>
+      <c r="F83">
+        <v>2.7783</v>
+      </c>
+      <c r="G83">
+        <v>0.365</v>
+      </c>
+      <c r="H83">
+        <v>0.62</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.57</v>
+      </c>
+      <c r="K83">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L83">
+        <v>1.41</v>
+      </c>
+      <c r="M83">
+        <v>0.13141359</v>
+      </c>
+      <c r="N83">
+        <v>1.27858641</v>
+      </c>
+      <c r="O83">
+        <v>0.2557172819999999</v>
+      </c>
+      <c r="P83">
+        <v>1.022869128</v>
+      </c>
+      <c r="Q83">
+        <v>1.182869128</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3703810025723344</v>
+      </c>
+      <c r="T83">
+        <v>4.153384100519114</v>
+      </c>
+      <c r="U83">
+        <v>0.0473</v>
+      </c>
+      <c r="V83">
+        <v>0.2</v>
+      </c>
+      <c r="W83">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>10.7294839141066</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1008628315615628</v>
+      </c>
+      <c r="C84">
+        <v>0.7335642472196127</v>
+      </c>
+      <c r="D84">
+        <v>3.181164247219613</v>
+      </c>
+      <c r="E84">
+        <v>0.002600000000000158</v>
+      </c>
+      <c r="F84">
+        <v>2.8126</v>
+      </c>
+      <c r="G84">
+        <v>0.365</v>
+      </c>
+      <c r="H84">
+        <v>0.62</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.57</v>
+      </c>
+      <c r="K84">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L84">
+        <v>1.41</v>
+      </c>
+      <c r="M84">
+        <v>0.13303598</v>
+      </c>
+      <c r="N84">
+        <v>1.27696402</v>
+      </c>
+      <c r="O84">
+        <v>0.2553928039999999</v>
+      </c>
+      <c r="P84">
+        <v>1.021571216</v>
+      </c>
+      <c r="Q84">
+        <v>1.181571216</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.387966842008682</v>
+      </c>
+      <c r="T84">
+        <v>4.373664349817396</v>
+      </c>
+      <c r="U84">
+        <v>0.0473</v>
+      </c>
+      <c r="V84">
+        <v>0.2</v>
+      </c>
+      <c r="W84">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>10.59863654930042</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.100702872634382</v>
+      </c>
+      <c r="C85">
+        <v>0.7012690856182089</v>
+      </c>
+      <c r="D85">
+        <v>3.183169085618209</v>
+      </c>
+      <c r="E85">
+        <v>0.03690000000000015</v>
+      </c>
+      <c r="F85">
+        <v>2.8469</v>
+      </c>
+      <c r="G85">
+        <v>0.365</v>
+      </c>
+      <c r="H85">
+        <v>0.62</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.57</v>
+      </c>
+      <c r="K85">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L85">
+        <v>1.41</v>
+      </c>
+      <c r="M85">
+        <v>0.13465837</v>
+      </c>
+      <c r="N85">
+        <v>1.27534163</v>
+      </c>
+      <c r="O85">
+        <v>0.2550683259999999</v>
+      </c>
+      <c r="P85">
+        <v>1.020273304</v>
+      </c>
+      <c r="Q85">
+        <v>1.180273304</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4076216037316588</v>
+      </c>
+      <c r="T85">
+        <v>4.619859922562536</v>
+      </c>
+      <c r="U85">
+        <v>0.0473</v>
+      </c>
+      <c r="V85">
+        <v>0.2</v>
+      </c>
+      <c r="W85">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>10.47094213304379</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1005429137072012</v>
+      </c>
+      <c r="C86">
+        <v>0.6689764525952673</v>
+      </c>
+      <c r="D86">
+        <v>3.185176452595267</v>
+      </c>
+      <c r="E86">
+        <v>0.07120000000000015</v>
+      </c>
+      <c r="F86">
+        <v>2.8812</v>
+      </c>
+      <c r="G86">
+        <v>0.365</v>
+      </c>
+      <c r="H86">
+        <v>0.62</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.57</v>
+      </c>
+      <c r="K86">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L86">
+        <v>1.41</v>
+      </c>
+      <c r="M86">
+        <v>0.13628076</v>
+      </c>
+      <c r="N86">
+        <v>1.27371924</v>
+      </c>
+      <c r="O86">
+        <v>0.2547438479999999</v>
+      </c>
+      <c r="P86">
+        <v>1.018975392</v>
+      </c>
+      <c r="Q86">
+        <v>1.178975392</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4297332106700074</v>
+      </c>
+      <c r="T86">
+        <v>4.896829941900815</v>
+      </c>
+      <c r="U86">
+        <v>0.0473</v>
+      </c>
+      <c r="V86">
+        <v>0.2</v>
+      </c>
+      <c r="W86">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>10.34628806003136</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1029669547800204</v>
+      </c>
+      <c r="C87">
+        <v>0.6045254728844527</v>
+      </c>
+      <c r="D87">
+        <v>3.155025472884453</v>
+      </c>
+      <c r="E87">
+        <v>0.1055000000000001</v>
+      </c>
+      <c r="F87">
+        <v>2.9155</v>
+      </c>
+      <c r="G87">
+        <v>0.365</v>
+      </c>
+      <c r="H87">
+        <v>0.62</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.57</v>
+      </c>
+      <c r="K87">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L87">
+        <v>1.41</v>
+      </c>
+      <c r="M87">
+        <v>0.14898205</v>
+      </c>
+      <c r="N87">
+        <v>1.26101795</v>
+      </c>
+      <c r="O87">
+        <v>0.2522035899999999</v>
+      </c>
+      <c r="P87">
+        <v>1.00881436</v>
+      </c>
+      <c r="Q87">
+        <v>1.16881436</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4547930318668028</v>
+      </c>
+      <c r="T87">
+        <v>5.210729297150867</v>
+      </c>
+      <c r="U87">
+        <v>0.0511</v>
+      </c>
+      <c r="V87">
+        <v>0.2</v>
+      </c>
+      <c r="W87">
+        <v>0.04088</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>9.464227401891703</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1028373958528397</v>
+      </c>
+      <c r="C88">
+        <v>0.5718225208196581</v>
+      </c>
+      <c r="D88">
+        <v>3.156622520819659</v>
+      </c>
+      <c r="E88">
+        <v>0.1398000000000001</v>
+      </c>
+      <c r="F88">
+        <v>2.9498</v>
+      </c>
+      <c r="G88">
+        <v>0.365</v>
+      </c>
+      <c r="H88">
+        <v>0.62</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.57</v>
+      </c>
+      <c r="K88">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L88">
+        <v>1.41</v>
+      </c>
+      <c r="M88">
+        <v>0.15073478</v>
+      </c>
+      <c r="N88">
+        <v>1.25926522</v>
+      </c>
+      <c r="O88">
+        <v>0.2518530439999999</v>
+      </c>
+      <c r="P88">
+        <v>1.007412176</v>
+      </c>
+      <c r="Q88">
+        <v>1.167412176</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4834328275202833</v>
+      </c>
+      <c r="T88">
+        <v>5.569471417436642</v>
+      </c>
+      <c r="U88">
+        <v>0.0511</v>
+      </c>
+      <c r="V88">
+        <v>0.2</v>
+      </c>
+      <c r="W88">
+        <v>0.04088</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>9.354178246055753</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1027078369256589</v>
+      </c>
+      <c r="C89">
+        <v>0.5391211863987508</v>
+      </c>
+      <c r="D89">
+        <v>3.158221186398751</v>
+      </c>
+      <c r="E89">
+        <v>0.1741000000000001</v>
+      </c>
+      <c r="F89">
+        <v>2.9841</v>
+      </c>
+      <c r="G89">
+        <v>0.365</v>
+      </c>
+      <c r="H89">
+        <v>0.62</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.57</v>
+      </c>
+      <c r="K89">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L89">
+        <v>1.41</v>
+      </c>
+      <c r="M89">
+        <v>0.15248751</v>
+      </c>
+      <c r="N89">
+        <v>1.25751249</v>
+      </c>
+      <c r="O89">
+        <v>0.2515024979999999</v>
+      </c>
+      <c r="P89">
+        <v>1.006009992</v>
+      </c>
+      <c r="Q89">
+        <v>1.166009992</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5164787455819914</v>
+      </c>
+      <c r="T89">
+        <v>5.983404633150996</v>
+      </c>
+      <c r="U89">
+        <v>0.0511</v>
+      </c>
+      <c r="V89">
+        <v>0.2</v>
+      </c>
+      <c r="W89">
+        <v>0.04088</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>9.246658955871203</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1025782779984781</v>
+      </c>
+      <c r="C90">
+        <v>0.5064214720807336</v>
+      </c>
+      <c r="D90">
+        <v>3.159821472080734</v>
+      </c>
+      <c r="E90">
+        <v>0.2084000000000001</v>
+      </c>
+      <c r="F90">
+        <v>3.0184</v>
+      </c>
+      <c r="G90">
+        <v>0.365</v>
+      </c>
+      <c r="H90">
+        <v>0.62</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.57</v>
+      </c>
+      <c r="K90">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L90">
+        <v>1.41</v>
+      </c>
+      <c r="M90">
+        <v>0.15424024</v>
+      </c>
+      <c r="N90">
+        <v>1.25575976</v>
+      </c>
+      <c r="O90">
+        <v>0.2511519519999999</v>
+      </c>
+      <c r="P90">
+        <v>1.004607808</v>
+      </c>
+      <c r="Q90">
+        <v>1.164607808</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5550323166539843</v>
+      </c>
+      <c r="T90">
+        <v>6.466326718151077</v>
+      </c>
+      <c r="U90">
+        <v>0.0511</v>
+      </c>
+      <c r="V90">
+        <v>0.2</v>
+      </c>
+      <c r="W90">
+        <v>0.04088</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>9.141583285918124</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1024487190712973</v>
+      </c>
+      <c r="C91">
+        <v>0.4737233803295982</v>
+      </c>
+      <c r="D91">
+        <v>3.161423380329598</v>
+      </c>
+      <c r="E91">
+        <v>0.2427000000000001</v>
+      </c>
+      <c r="F91">
+        <v>3.0527</v>
+      </c>
+      <c r="G91">
+        <v>0.365</v>
+      </c>
+      <c r="H91">
+        <v>0.62</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.57</v>
+      </c>
+      <c r="K91">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L91">
+        <v>1.41</v>
+      </c>
+      <c r="M91">
+        <v>0.15599297</v>
+      </c>
+      <c r="N91">
+        <v>1.25400703</v>
+      </c>
+      <c r="O91">
+        <v>0.2508014059999999</v>
+      </c>
+      <c r="P91">
+        <v>1.003205624</v>
+      </c>
+      <c r="Q91">
+        <v>1.163205624</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6005956279208848</v>
+      </c>
+      <c r="T91">
+        <v>7.037052818605718</v>
+      </c>
+      <c r="U91">
+        <v>0.0511</v>
+      </c>
+      <c r="V91">
+        <v>0.2</v>
+      </c>
+      <c r="W91">
+        <v>0.04088</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>9.038868866975223</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1023191601441166</v>
+      </c>
+      <c r="C92">
+        <v>0.4410269136143312</v>
+      </c>
+      <c r="D92">
+        <v>3.163026913614331</v>
+      </c>
+      <c r="E92">
+        <v>0.2770000000000001</v>
+      </c>
+      <c r="F92">
+        <v>3.087</v>
+      </c>
+      <c r="G92">
+        <v>0.365</v>
+      </c>
+      <c r="H92">
+        <v>0.62</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.57</v>
+      </c>
+      <c r="K92">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L92">
+        <v>1.41</v>
+      </c>
+      <c r="M92">
+        <v>0.1577457</v>
+      </c>
+      <c r="N92">
+        <v>1.2522543</v>
+      </c>
+      <c r="O92">
+        <v>0.2504508599999999</v>
+      </c>
+      <c r="P92">
+        <v>1.00180344</v>
+      </c>
+      <c r="Q92">
+        <v>1.16180344</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6552716014411659</v>
+      </c>
+      <c r="T92">
+        <v>7.721924139151288</v>
+      </c>
+      <c r="U92">
+        <v>0.0511</v>
+      </c>
+      <c r="V92">
+        <v>0.2</v>
+      </c>
+      <c r="W92">
+        <v>0.04088</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>8.938436990675498</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1021896012169358</v>
+      </c>
+      <c r="C93">
+        <v>0.4083320744089352</v>
+      </c>
+      <c r="D93">
+        <v>3.164632074408936</v>
+      </c>
+      <c r="E93">
+        <v>0.3113000000000001</v>
+      </c>
+      <c r="F93">
+        <v>3.1213</v>
+      </c>
+      <c r="G93">
+        <v>0.365</v>
+      </c>
+      <c r="H93">
+        <v>0.62</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.57</v>
+      </c>
+      <c r="K93">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L93">
+        <v>1.41</v>
+      </c>
+      <c r="M93">
+        <v>0.15949843</v>
+      </c>
+      <c r="N93">
+        <v>1.25050157</v>
+      </c>
+      <c r="O93">
+        <v>0.2501003139999999</v>
+      </c>
+      <c r="P93">
+        <v>1.000401256</v>
+      </c>
+      <c r="Q93">
+        <v>1.160401256</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7220977912992868</v>
+      </c>
+      <c r="T93">
+        <v>8.558989086484761</v>
+      </c>
+      <c r="U93">
+        <v>0.0511</v>
+      </c>
+      <c r="V93">
+        <v>0.2</v>
+      </c>
+      <c r="W93">
+        <v>0.04088</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>8.840212408360383</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.102060042289755</v>
+      </c>
+      <c r="C94">
+        <v>0.3756388651924349</v>
+      </c>
+      <c r="D94">
+        <v>3.166238865192435</v>
+      </c>
+      <c r="E94">
+        <v>0.3456000000000001</v>
+      </c>
+      <c r="F94">
+        <v>3.1556</v>
+      </c>
+      <c r="G94">
+        <v>0.365</v>
+      </c>
+      <c r="H94">
+        <v>0.62</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.57</v>
+      </c>
+      <c r="K94">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L94">
+        <v>1.41</v>
+      </c>
+      <c r="M94">
+        <v>0.16125116</v>
+      </c>
+      <c r="N94">
+        <v>1.24874884</v>
+      </c>
+      <c r="O94">
+        <v>0.2497497679999999</v>
+      </c>
+      <c r="P94">
+        <v>0.998999072</v>
+      </c>
+      <c r="Q94">
+        <v>1.158999072</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8056305286219383</v>
+      </c>
+      <c r="T94">
+        <v>9.605320270651605</v>
+      </c>
+      <c r="U94">
+        <v>0.0511</v>
+      </c>
+      <c r="V94">
+        <v>0.2</v>
+      </c>
+      <c r="W94">
+        <v>0.04088</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>8.744123143052118</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1019304833625742</v>
+      </c>
+      <c r="C95">
+        <v>0.3429472884488942</v>
+      </c>
+      <c r="D95">
+        <v>3.167847288448895</v>
+      </c>
+      <c r="E95">
+        <v>0.3799000000000001</v>
+      </c>
+      <c r="F95">
+        <v>3.1899</v>
+      </c>
+      <c r="G95">
+        <v>0.365</v>
+      </c>
+      <c r="H95">
+        <v>0.62</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.57</v>
+      </c>
+      <c r="K95">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L95">
+        <v>1.41</v>
+      </c>
+      <c r="M95">
+        <v>0.16300389</v>
+      </c>
+      <c r="N95">
+        <v>1.24699611</v>
+      </c>
+      <c r="O95">
+        <v>0.2493992219999999</v>
+      </c>
+      <c r="P95">
+        <v>0.997596888</v>
+      </c>
+      <c r="Q95">
+        <v>1.157596888</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9130297623224899</v>
+      </c>
+      <c r="T95">
+        <v>10.95060322172326</v>
+      </c>
+      <c r="U95">
+        <v>0.0511</v>
+      </c>
+      <c r="V95">
+        <v>0.2</v>
+      </c>
+      <c r="W95">
+        <v>0.04088</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>8.650100313556933</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1018009244353935</v>
+      </c>
+      <c r="C96">
+        <v>0.310257346667425</v>
+      </c>
+      <c r="D96">
+        <v>3.169457346667425</v>
+      </c>
+      <c r="E96">
+        <v>0.4142000000000001</v>
+      </c>
+      <c r="F96">
+        <v>3.2242</v>
+      </c>
+      <c r="G96">
+        <v>0.365</v>
+      </c>
+      <c r="H96">
+        <v>0.62</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.57</v>
+      </c>
+      <c r="K96">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L96">
+        <v>1.41</v>
+      </c>
+      <c r="M96">
+        <v>0.16475662</v>
+      </c>
+      <c r="N96">
+        <v>1.24524338</v>
+      </c>
+      <c r="O96">
+        <v>0.2490486759999999</v>
+      </c>
+      <c r="P96">
+        <v>0.9961947039999999</v>
+      </c>
+      <c r="Q96">
+        <v>1.156194704</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.056228740589892</v>
+      </c>
+      <c r="T96">
+        <v>12.74431382315213</v>
+      </c>
+      <c r="U96">
+        <v>0.0511</v>
+      </c>
+      <c r="V96">
+        <v>0.2</v>
+      </c>
+      <c r="W96">
+        <v>0.04088</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>8.558077969795688</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1016713655082127</v>
+      </c>
+      <c r="C97">
+        <v>0.2775690423422037</v>
+      </c>
+      <c r="D97">
+        <v>3.171069042342204</v>
+      </c>
+      <c r="E97">
+        <v>0.4485000000000001</v>
+      </c>
+      <c r="F97">
+        <v>3.2585</v>
+      </c>
+      <c r="G97">
+        <v>0.365</v>
+      </c>
+      <c r="H97">
+        <v>0.62</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.57</v>
+      </c>
+      <c r="K97">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L97">
+        <v>1.41</v>
+      </c>
+      <c r="M97">
+        <v>0.16650935</v>
+      </c>
+      <c r="N97">
+        <v>1.24349065</v>
+      </c>
+      <c r="O97">
+        <v>0.24869813</v>
+      </c>
+      <c r="P97">
+        <v>0.9947925200000001</v>
+      </c>
+      <c r="Q97">
+        <v>1.15479252</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.256707310164256</v>
+      </c>
+      <c r="T97">
+        <v>15.25550866515256</v>
+      </c>
+      <c r="U97">
+        <v>0.0511</v>
+      </c>
+      <c r="V97">
+        <v>0.2</v>
+      </c>
+      <c r="W97">
+        <v>0.04088</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>8.467992938534683</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1015418065810319</v>
+      </c>
+      <c r="C98">
+        <v>0.2448823779724809</v>
+      </c>
+      <c r="D98">
+        <v>3.172682377972481</v>
+      </c>
+      <c r="E98">
+        <v>0.4828000000000001</v>
+      </c>
+      <c r="F98">
+        <v>3.2928</v>
+      </c>
+      <c r="G98">
+        <v>0.365</v>
+      </c>
+      <c r="H98">
+        <v>0.62</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.57</v>
+      </c>
+      <c r="K98">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L98">
+        <v>1.41</v>
+      </c>
+      <c r="M98">
+        <v>0.16826208</v>
+      </c>
+      <c r="N98">
+        <v>1.24173792</v>
+      </c>
+      <c r="O98">
+        <v>0.2483475839999999</v>
+      </c>
+      <c r="P98">
+        <v>0.9933903359999999</v>
+      </c>
+      <c r="Q98">
+        <v>1.153390336</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.557425164525797</v>
+      </c>
+      <c r="T98">
+        <v>19.02230092815315</v>
+      </c>
+      <c r="U98">
+        <v>0.0511</v>
+      </c>
+      <c r="V98">
+        <v>0.2</v>
+      </c>
+      <c r="W98">
+        <v>0.04088</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>8.379784678758279</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1014122476538512</v>
+      </c>
+      <c r="C99">
+        <v>0.2121973560625983</v>
+      </c>
+      <c r="D99">
+        <v>3.174297356062599</v>
+      </c>
+      <c r="E99">
+        <v>0.5171000000000001</v>
+      </c>
+      <c r="F99">
+        <v>3.3271</v>
+      </c>
+      <c r="G99">
+        <v>0.365</v>
+      </c>
+      <c r="H99">
+        <v>0.62</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.57</v>
+      </c>
+      <c r="K99">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L99">
+        <v>1.41</v>
+      </c>
+      <c r="M99">
+        <v>0.17001481</v>
+      </c>
+      <c r="N99">
+        <v>1.23998519</v>
+      </c>
+      <c r="O99">
+        <v>0.2479970379999999</v>
+      </c>
+      <c r="P99">
+        <v>0.9919881519999999</v>
+      </c>
+      <c r="Q99">
+        <v>1.151988152</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.058621588461704</v>
+      </c>
+      <c r="T99">
+        <v>25.30028803315419</v>
+      </c>
+      <c r="U99">
+        <v>0.0511</v>
+      </c>
+      <c r="V99">
+        <v>0.2</v>
+      </c>
+      <c r="W99">
+        <v>0.04088</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>8.293395145987574</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1012826887266704</v>
+      </c>
+      <c r="C100">
+        <v>0.1795139791219982</v>
+      </c>
+      <c r="D100">
+        <v>3.175913979121999</v>
+      </c>
+      <c r="E100">
+        <v>0.5514000000000001</v>
+      </c>
+      <c r="F100">
+        <v>3.3614</v>
+      </c>
+      <c r="G100">
+        <v>0.365</v>
+      </c>
+      <c r="H100">
+        <v>0.62</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.57</v>
+      </c>
+      <c r="K100">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L100">
+        <v>1.41</v>
+      </c>
+      <c r="M100">
+        <v>0.17176754</v>
+      </c>
+      <c r="N100">
+        <v>1.23823246</v>
+      </c>
+      <c r="O100">
+        <v>0.2476464919999999</v>
+      </c>
+      <c r="P100">
+        <v>0.990585968</v>
+      </c>
+      <c r="Q100">
+        <v>1.150585968</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.061014436333517</v>
+      </c>
+      <c r="T100">
+        <v>37.85626224315627</v>
+      </c>
+      <c r="U100">
+        <v>0.0511</v>
+      </c>
+      <c r="V100">
+        <v>0.2</v>
+      </c>
+      <c r="W100">
+        <v>0.04088</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>8.208768664906071</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1011531297994896</v>
+      </c>
+      <c r="C101">
+        <v>0.1468322496652354</v>
+      </c>
+      <c r="D101">
+        <v>3.177532249665236</v>
+      </c>
+      <c r="E101">
+        <v>0.5857000000000001</v>
+      </c>
+      <c r="F101">
+        <v>3.3957</v>
+      </c>
+      <c r="G101">
+        <v>0.365</v>
+      </c>
+      <c r="H101">
+        <v>0.62</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.57</v>
+      </c>
+      <c r="K101">
+        <v>0.1600000000000001</v>
+      </c>
+      <c r="L101">
+        <v>1.41</v>
+      </c>
+      <c r="M101">
+        <v>0.17352027</v>
+      </c>
+      <c r="N101">
+        <v>1.23647973</v>
+      </c>
+      <c r="O101">
+        <v>0.2472959459999999</v>
+      </c>
+      <c r="P101">
+        <v>0.989183784</v>
+      </c>
+      <c r="Q101">
+        <v>1.149183784</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.068192979948956</v>
+      </c>
+      <c r="T101">
+        <v>75.52418487316251</v>
+      </c>
+      <c r="U101">
+        <v>0.0511</v>
+      </c>
+      <c r="V101">
+        <v>0.2</v>
+      </c>
+      <c r="W101">
+        <v>0.04088</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>8.125851809704997</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
